--- a/eXCEL.xlsx
+++ b/eXCEL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E168AD3-23C1-CC49-9F00-86B9822D7091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2AC8A7-D47C-8B48-AA27-2040460B41CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="500" windowWidth="15420" windowHeight="14020" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -19,16 +19,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$3:$K$15</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$J$3</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$J$4:$J$15</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$3</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$K$4:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$52:$S$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId5"/>
-    <pivotCache cacheId="28" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -69,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
   <si>
     <t>Sno</t>
   </si>
@@ -257,9 +253,6 @@
     <t>Column4</t>
   </si>
   <si>
-    <t>Column5</t>
-  </si>
-  <si>
     <t>Column6</t>
   </si>
   <si>
@@ -291,16 +284,122 @@
   </si>
   <si>
     <t>Column12</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M </t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>doj</t>
+  </si>
+  <si>
+    <t>Expence_Name</t>
+  </si>
+  <si>
+    <t>Costing</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Exp_1</t>
+  </si>
+  <si>
+    <t>Exp_2</t>
+  </si>
+  <si>
+    <t>Exp_3</t>
+  </si>
+  <si>
+    <t>Exp_4</t>
+  </si>
+  <si>
+    <t>Exp_5</t>
+  </si>
+  <si>
+    <t>Exp_6</t>
+  </si>
+  <si>
+    <t>Exp_7</t>
+  </si>
+  <si>
+    <t>Exp_8</t>
+  </si>
+  <si>
+    <t>Exp_9</t>
+  </si>
+  <si>
+    <t>Exp_10</t>
+  </si>
+  <si>
+    <t>Exp_11</t>
+  </si>
+  <si>
+    <t>Exp_12</t>
+  </si>
+  <si>
+    <t>Exp_13</t>
+  </si>
+  <si>
+    <t>Exp_14</t>
+  </si>
+  <si>
+    <t>Exp_15</t>
+  </si>
+  <si>
+    <t>Exp_16</t>
+  </si>
+  <si>
+    <t>Exp_17</t>
+  </si>
+  <si>
+    <t>Exp_18</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Total_Count:</t>
+  </si>
+  <si>
+    <t>Total_Budget:</t>
+  </si>
+  <si>
+    <t>Total_Cost:</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Savings:</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>DASH_BOARD 101(Expence Tracker)</t>
+  </si>
+  <si>
+    <t>Remarks:</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -367,8 +466,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="45"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,8 +576,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -591,12 +738,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -613,18 +771,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -667,9 +813,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -693,81 +836,97 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="29">
     <dxf>
       <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -1022,6 +1181,136 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2503,6 +2792,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2534,6 +2828,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2565,6 +2864,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -2596,6 +2900,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -2627,6 +2936,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -2698,6 +3012,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -2732,6 +3051,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -2766,6 +3090,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -2800,6 +3129,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -2834,6 +3168,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -2868,6 +3207,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:val>
             <c:numRef>
@@ -2964,6 +3308,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2995,6 +3344,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3026,6 +3380,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3057,6 +3416,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -3088,6 +3452,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -3119,6 +3488,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -3153,6 +3527,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -3187,6 +3566,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -3221,6 +3605,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -3255,6 +3644,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -3289,6 +3683,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -3323,6 +3722,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-BEEF-F747-9615-BB52863B3925}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:val>
             <c:numRef>
@@ -6187,7 +6591,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" numFmtId="2" showAll="0">
@@ -6302,7 +6706,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -6343,27 +6747,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A2:L15" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="Column5" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="doj" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="4">
       <calculatedColumnFormula>SUM(F3+G3+H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="9">
+    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="3">
       <calculatedColumnFormula>AVERAGE(F3:H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="2">
       <calculatedColumnFormula>CONCATENATE(B3,"  ",C3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="1">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6752,12 +7156,12 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B4" t="s">
@@ -6783,67 +7187,67 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+      <c r="A5" s="14">
         <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="14">
         <v>1600</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="14">
         <v>1700</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="14">
         <v>1800</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+      <c r="A9" s="14">
         <v>1900</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="14">
         <v>2000</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="18">
+      <c r="A11" s="14">
         <v>2100</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="14">
         <v>2200</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+      <c r="A13" s="14">
         <v>2300</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="14">
         <v>2400</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="18">
+      <c r="A15" s="14">
         <v>2500</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="14">
         <v>2600</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="14" t="s">
         <v>56</v>
       </c>
     </row>
@@ -6862,7 +7266,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B1" t="s">
@@ -6877,30 +7281,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
-  <dimension ref="A1:AE40"/>
+  <dimension ref="A1:AE79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="10" max="10" width="11.6640625" customWidth="1"/>
-    <col min="11" max="11" width="22.1640625" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
       <c r="Y1" s="3" t="s">
         <v>1</v>
       </c>
@@ -6909,48 +7314,48 @@
       </c>
     </row>
     <row r="2" spans="1:31" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="G2" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="H2" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="I2" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="46" t="s">
+      <c r="L2" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="48"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="43"/>
       <c r="U2" s="8" t="s">
         <v>42</v>
       </c>
@@ -6965,10 +7370,10 @@
       <c r="AB2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AE2" s="15"/>
+      <c r="AE2" s="11"/>
     </row>
     <row r="3" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -6977,7 +7382,9 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="50" t="s">
+        <v>73</v>
+      </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,10 +7403,10 @@
       <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="33" t="str">
+      <c r="L3" s="28" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
@@ -7013,7 +7420,7 @@
         <v>36</v>
       </c>
       <c r="AA3" s="6">
-        <f>AVERAGE(F4:H4)</f>
+        <f t="shared" ref="AA3:AA14" si="0">AVERAGE(F4:H4)</f>
         <v>1500</v>
       </c>
       <c r="AB3" s="1" t="str">
@@ -7022,7 +7429,7 @@
       </c>
     </row>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -7031,7 +7438,9 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E4" s="5">
         <v>23</v>
       </c>
@@ -7045,18 +7454,18 @@
         <v>1500</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" ref="I4:I15" si="0">SUM(F4+G4+H4)</f>
+        <f t="shared" ref="I4:I15" si="1">SUM(F4+G4+H4)</f>
         <v>4500</v>
       </c>
       <c r="J4" s="6">
         <f>AVERAGE(F4:H4)</f>
         <v>1500</v>
       </c>
-      <c r="K4" s="23" t="str">
-        <f t="shared" ref="K4:K15" si="1">CONCATENATE(B4,"  ",C4)</f>
+      <c r="K4" s="19" t="str">
+        <f>CONCATENATE(B4,"  ",C4)</f>
         <v>A  X</v>
       </c>
-      <c r="L4" s="45" t="str">
+      <c r="L4" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Bad</v>
       </c>
@@ -7088,7 +7497,7 @@
         <v>9</v>
       </c>
       <c r="AA4" s="6">
-        <f>AVERAGE(F5:H5)</f>
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="AB4" s="1" t="str">
@@ -7097,7 +7506,7 @@
       </c>
     </row>
     <row r="5" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -7106,7 +7515,9 @@
       <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E5" s="5">
         <v>24</v>
       </c>
@@ -7120,18 +7531,18 @@
         <v>1600</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="J5" s="6">
         <f t="shared" ref="J5:J15" si="2">AVERAGE(F5:H5)</f>
         <v>1600</v>
       </c>
-      <c r="K5" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K5" s="19" t="str">
+        <f>CONCATENATE(B5,"  ",C5)</f>
         <v>ghg  hg</v>
       </c>
-      <c r="L5" s="45" t="str">
+      <c r="L5" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Bad</v>
       </c>
@@ -7166,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="AA5" s="6">
-        <f>AVERAGE(F6:H6)</f>
+        <f t="shared" si="0"/>
         <v>1700</v>
       </c>
       <c r="AB5" s="1" t="str">
@@ -7175,7 +7586,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -7184,7 +7595,9 @@
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E6" s="5">
         <v>25</v>
       </c>
@@ -7198,18 +7611,18 @@
         <v>1700</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5100</v>
       </c>
       <c r="J6" s="6">
         <f t="shared" si="2"/>
         <v>1700</v>
       </c>
-      <c r="K6" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K6" s="19" t="str">
+        <f>CONCATENATE(B6,"  ",C6)</f>
         <v>A  X</v>
       </c>
-      <c r="L6" s="45" t="str">
+      <c r="L6" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Bad</v>
       </c>
@@ -7244,7 +7657,7 @@
         <v>36</v>
       </c>
       <c r="AA6" s="6">
-        <f>AVERAGE(F7:H7)</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="AB6" s="1" t="str">
@@ -7253,7 +7666,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+      <c r="A7" s="17">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -7262,7 +7675,9 @@
       <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E7" s="5">
         <v>26</v>
       </c>
@@ -7276,18 +7691,18 @@
         <v>1800</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5400</v>
       </c>
       <c r="J7" s="6">
         <f t="shared" si="2"/>
         <v>1800</v>
       </c>
-      <c r="K7" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K7" s="19" t="str">
+        <f>CONCATENATE(B7,"  ",C7)</f>
         <v>B  Y</v>
       </c>
-      <c r="L7" s="45" t="str">
+      <c r="L7" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Bad</v>
       </c>
@@ -7322,7 +7737,7 @@
         <v>14</v>
       </c>
       <c r="AA7" s="6">
-        <f>AVERAGE(F8:H8)</f>
+        <f t="shared" si="0"/>
         <v>1900</v>
       </c>
       <c r="AB7" s="1" t="str">
@@ -7331,7 +7746,7 @@
       </c>
     </row>
     <row r="8" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21">
+      <c r="A8" s="17">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -7340,7 +7755,9 @@
       <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E8" s="5">
         <v>27</v>
       </c>
@@ -7354,18 +7771,18 @@
         <v>1900</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5700</v>
       </c>
       <c r="J8" s="6">
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="K8" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K8" s="19" t="str">
+        <f>CONCATENATE(B8,"  ",C8)</f>
         <v>ghg  hggh</v>
       </c>
-      <c r="L8" s="45" t="str">
+      <c r="L8" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
@@ -7400,7 +7817,7 @@
         <v>9</v>
       </c>
       <c r="AA8" s="6">
-        <f>AVERAGE(F9:H9)</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="AB8" s="1" t="str">
@@ -7409,7 +7826,7 @@
       </c>
     </row>
     <row r="9" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -7418,7 +7835,9 @@
       <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E9" s="5">
         <v>28</v>
       </c>
@@ -7432,18 +7851,18 @@
         <v>2000</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
       <c r="J9" s="6">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="K9" s="24" t="str">
-        <f t="shared" si="1"/>
+      <c r="K9" s="20" t="str">
+        <f>CONCATENATE(B9,"  ",C9)</f>
         <v>c  v</v>
       </c>
-      <c r="L9" s="45" t="str">
+      <c r="L9" s="40" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
@@ -7478,7 +7897,7 @@
         <v>16</v>
       </c>
       <c r="AA9" s="6">
-        <f>AVERAGE(F10:H10)</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="AB9" s="1" t="str">
@@ -7487,7 +7906,7 @@
       </c>
     </row>
     <row r="10" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
+      <c r="A10" s="17">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -7496,7 +7915,9 @@
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E10" s="5">
         <v>29</v>
       </c>
@@ -7510,15 +7931,15 @@
         <v>2100</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6300</v>
       </c>
       <c r="J10" s="6">
         <f t="shared" si="2"/>
         <v>2100</v>
       </c>
-      <c r="K10" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K10" s="19" t="str">
+        <f>CONCATENATE(B10,"  ",C10)</f>
         <v>A  X</v>
       </c>
       <c r="L10" s="6" t="str">
@@ -7541,7 +7962,7 @@
         <v>9</v>
       </c>
       <c r="AA10" s="6">
-        <f>AVERAGE(F11:H11)</f>
+        <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="AB10" s="1" t="str">
@@ -7550,7 +7971,7 @@
       </c>
     </row>
     <row r="11" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -7559,7 +7980,9 @@
       <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
@@ -7573,15 +7996,15 @@
         <v>2200</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6600</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="2"/>
         <v>2200</v>
       </c>
-      <c r="K11" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K11" s="19" t="str">
+        <f>CONCATENATE(B11,"  ",C11)</f>
         <v>k  Y</v>
       </c>
       <c r="L11" s="6" t="str">
@@ -7604,7 +8027,7 @@
         <v>10</v>
       </c>
       <c r="AA11" s="6">
-        <f>AVERAGE(F12:H12)</f>
+        <f t="shared" si="0"/>
         <v>2300</v>
       </c>
       <c r="AB11" s="1" t="str">
@@ -7613,7 +8036,7 @@
       </c>
     </row>
     <row r="12" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
+      <c r="A12" s="17">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -7622,7 +8045,9 @@
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E12" s="5">
         <v>31</v>
       </c>
@@ -7636,15 +8061,15 @@
         <v>2300</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6900</v>
       </c>
       <c r="J12" s="6">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="K12" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K12" s="19" t="str">
+        <f>CONCATENATE(B12,"  ",C12)</f>
         <v>A  X</v>
       </c>
       <c r="L12" s="6" t="str">
@@ -7667,7 +8092,7 @@
         <v>9</v>
       </c>
       <c r="AA12" s="6">
-        <f>AVERAGE(F13:H13)</f>
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="AB12" s="1" t="str">
@@ -7676,7 +8101,7 @@
       </c>
     </row>
     <row r="13" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="21">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -7685,7 +8110,9 @@
       <c r="C13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="E13" s="5">
         <v>32</v>
       </c>
@@ -7699,15 +8126,15 @@
         <v>2400</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7200</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="2"/>
         <v>2400</v>
       </c>
-      <c r="K13" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K13" s="19" t="str">
+        <f>CONCATENATE(B13,"  ",C13)</f>
         <v>B  Y</v>
       </c>
       <c r="L13" s="6" t="str">
@@ -7718,7 +8145,7 @@
         <v>10</v>
       </c>
       <c r="AA13" s="6">
-        <f>AVERAGE(F14:H14)</f>
+        <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="AB13" s="1" t="str">
@@ -7727,7 +8154,7 @@
       </c>
     </row>
     <row r="14" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -7736,7 +8163,9 @@
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E14" s="5">
         <v>33</v>
       </c>
@@ -7750,15 +8179,15 @@
         <v>2500</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7500</v>
       </c>
       <c r="J14" s="6">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="K14" s="23" t="str">
-        <f t="shared" si="1"/>
+      <c r="K14" s="19" t="str">
+        <f>CONCATENATE(B14,"  ",C14)</f>
         <v>A  X</v>
       </c>
       <c r="L14" s="6" t="str">
@@ -7766,7 +8195,7 @@
         <v>Good</v>
       </c>
       <c r="AA14" s="6">
-        <f>AVERAGE(F15:H15)</f>
+        <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="AB14" s="1" t="str">
@@ -7775,84 +8204,86 @@
       </c>
     </row>
     <row r="15" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25">
+      <c r="A15" s="21">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27">
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="23">
         <v>34</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="24">
         <v>2600</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="24">
         <v>2600</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="24">
         <v>2600</v>
       </c>
-      <c r="I15" s="28">
-        <f t="shared" si="0"/>
+      <c r="I15" s="24">
+        <f t="shared" si="1"/>
         <v>7800</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="24">
         <f t="shared" si="2"/>
         <v>2600</v>
       </c>
-      <c r="K15" s="29" t="str">
-        <f t="shared" si="1"/>
+      <c r="K15" s="25" t="str">
+        <f>CONCATENATE(B15,"  ",C15)</f>
         <v>B  Y</v>
       </c>
-      <c r="L15" s="28" t="str">
+      <c r="L15" s="24" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="16">
+      <c r="F16" s="48"/>
+      <c r="G16" s="12">
         <f t="shared" ref="G16:I16" si="3">SUM(G4:G15)</f>
         <v>24600</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="12">
         <f t="shared" si="3"/>
         <v>24600</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="12">
         <f t="shared" si="3"/>
         <v>73800</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="12">
         <f>SUM(J4:J15)</f>
         <v>24600</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E17" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="19">
+      <c r="E17" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="49"/>
+      <c r="G17" s="15">
         <f>+COUNT(G4:G15)</f>
         <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I17">
         <f>COUNTA(K4:K15)</f>
         <v>12</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <f>J4+J5+J6+J7+J8+J9</f>
         <v>10500</v>
       </c>
@@ -7866,69 +8297,69 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E18" s="32"/>
-      <c r="F18" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="18">
+      <c r="E18" s="27"/>
+      <c r="F18" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="14">
         <f>MIN(J4:J15)</f>
         <v>1500</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="16">
+        <v>71</v>
+      </c>
+      <c r="I18" s="12">
         <f>MAX(J4:J15)</f>
         <v>2600</v>
       </c>
-      <c r="K18" s="16"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="19"/>
-      <c r="K19" s="16"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="15"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
     </row>
     <row r="22" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="44"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="43"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="38"/>
     </row>
     <row r="23" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
     </row>
     <row r="24" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7943,22 +8374,945 @@
     <row r="30" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
+      <c r="R47" s="65"/>
+      <c r="S47" s="65"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="65"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A49" s="65"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="65"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A52" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
+      <c r="L52" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="M52" s="56"/>
+      <c r="N52" s="56"/>
+      <c r="O52" s="56"/>
+      <c r="P52" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q52" s="56"/>
+      <c r="R52" s="56"/>
+      <c r="S52" s="56"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A53" s="56"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="56"/>
+      <c r="N53" s="56"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="56"/>
+    </row>
+    <row r="54" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="54">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="64">
+        <v>1200</v>
+      </c>
+      <c r="I54" s="64"/>
+      <c r="J54" s="64"/>
+      <c r="K54" s="64"/>
+      <c r="L54" s="62">
+        <f>E54-H54</f>
+        <v>-200</v>
+      </c>
+      <c r="M54" s="63"/>
+      <c r="N54" s="63"/>
+      <c r="O54" s="63"/>
+      <c r="P54" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q54" s="60"/>
+      <c r="R54" s="60"/>
+      <c r="S54" s="60"/>
+    </row>
+    <row r="55" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="54">
+        <v>2000</v>
+      </c>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54">
+        <v>1300</v>
+      </c>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="62">
+        <f t="shared" ref="L55:L71" si="4">E55-H55</f>
+        <v>700</v>
+      </c>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q55" s="61"/>
+      <c r="R55" s="61"/>
+      <c r="S55" s="61"/>
+    </row>
+    <row r="56" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="54">
+        <v>3000</v>
+      </c>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54">
+        <v>1400</v>
+      </c>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="62">
+        <f t="shared" si="4"/>
+        <v>1600</v>
+      </c>
+      <c r="M56" s="63"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="63"/>
+      <c r="P56" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q56" s="61"/>
+      <c r="R56" s="61"/>
+      <c r="S56" s="61"/>
+    </row>
+    <row r="57" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="54">
+        <v>4000</v>
+      </c>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54">
+        <v>1500</v>
+      </c>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="62">
+        <f t="shared" si="4"/>
+        <v>2500</v>
+      </c>
+      <c r="M57" s="63"/>
+      <c r="N57" s="63"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="61"/>
+      <c r="S57" s="61"/>
+    </row>
+    <row r="58" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="54">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54">
+        <v>1600</v>
+      </c>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="62">
+        <f t="shared" si="4"/>
+        <v>3400</v>
+      </c>
+      <c r="M58" s="63"/>
+      <c r="N58" s="63"/>
+      <c r="O58" s="63"/>
+      <c r="P58" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="61"/>
+      <c r="S58" s="61"/>
+    </row>
+    <row r="59" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A59" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="54">
+        <v>6000</v>
+      </c>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54">
+        <v>1700</v>
+      </c>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="54"/>
+      <c r="L59" s="62">
+        <f t="shared" si="4"/>
+        <v>4300</v>
+      </c>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q59" s="61"/>
+      <c r="R59" s="61"/>
+      <c r="S59" s="61"/>
+    </row>
+    <row r="60" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="54">
+        <v>7000</v>
+      </c>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54">
+        <v>1800</v>
+      </c>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="62">
+        <f t="shared" si="4"/>
+        <v>5200</v>
+      </c>
+      <c r="M60" s="63"/>
+      <c r="N60" s="63"/>
+      <c r="O60" s="63"/>
+      <c r="P60" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q60" s="61"/>
+      <c r="R60" s="61"/>
+      <c r="S60" s="61"/>
+    </row>
+    <row r="61" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="54">
+        <v>8000</v>
+      </c>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54">
+        <v>1900</v>
+      </c>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="62">
+        <f t="shared" si="4"/>
+        <v>6100</v>
+      </c>
+      <c r="M61" s="63"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="63"/>
+      <c r="P61" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q61" s="61"/>
+      <c r="R61" s="61"/>
+      <c r="S61" s="61"/>
+    </row>
+    <row r="62" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="54">
+        <v>9000</v>
+      </c>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54">
+        <v>2000</v>
+      </c>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="62">
+        <f t="shared" si="4"/>
+        <v>7000</v>
+      </c>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="63"/>
+      <c r="P62" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q62" s="61"/>
+      <c r="R62" s="61"/>
+      <c r="S62" s="61"/>
+    </row>
+    <row r="63" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="54">
+        <v>10000</v>
+      </c>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="54">
+        <v>22100</v>
+      </c>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="62">
+        <f t="shared" si="4"/>
+        <v>-12100</v>
+      </c>
+      <c r="M63" s="63"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="63"/>
+      <c r="P63" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q63" s="60"/>
+      <c r="R63" s="60"/>
+      <c r="S63" s="60"/>
+    </row>
+    <row r="64" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="54">
+        <v>11000</v>
+      </c>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54">
+        <v>2200</v>
+      </c>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="62">
+        <f t="shared" si="4"/>
+        <v>8800</v>
+      </c>
+      <c r="M64" s="63"/>
+      <c r="N64" s="63"/>
+      <c r="O64" s="63"/>
+      <c r="P64" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q64" s="61"/>
+      <c r="R64" s="61"/>
+      <c r="S64" s="61"/>
+    </row>
+    <row r="65" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="54">
+        <v>12000</v>
+      </c>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54">
+        <v>22300</v>
+      </c>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="54"/>
+      <c r="L65" s="62">
+        <f t="shared" si="4"/>
+        <v>-10300</v>
+      </c>
+      <c r="M65" s="63"/>
+      <c r="N65" s="63"/>
+      <c r="O65" s="63"/>
+      <c r="P65" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+    </row>
+    <row r="66" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="58"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="54">
+        <v>13000</v>
+      </c>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
+      <c r="H66" s="54">
+        <v>22400</v>
+      </c>
+      <c r="I66" s="54"/>
+      <c r="J66" s="54"/>
+      <c r="K66" s="54"/>
+      <c r="L66" s="62">
+        <f t="shared" si="4"/>
+        <v>-9400</v>
+      </c>
+      <c r="M66" s="63"/>
+      <c r="N66" s="63"/>
+      <c r="O66" s="63"/>
+      <c r="P66" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+    </row>
+    <row r="67" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="54">
+        <v>14000</v>
+      </c>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54">
+        <v>2500</v>
+      </c>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
+      <c r="K67" s="54"/>
+      <c r="L67" s="62">
+        <f t="shared" si="4"/>
+        <v>11500</v>
+      </c>
+      <c r="M67" s="63"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="63"/>
+      <c r="P67" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q67" s="61"/>
+      <c r="R67" s="61"/>
+      <c r="S67" s="61"/>
+    </row>
+    <row r="68" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="54">
+        <v>15000</v>
+      </c>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54">
+        <v>2600</v>
+      </c>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="54"/>
+      <c r="L68" s="62">
+        <f t="shared" si="4"/>
+        <v>12400</v>
+      </c>
+      <c r="M68" s="63"/>
+      <c r="N68" s="63"/>
+      <c r="O68" s="63"/>
+      <c r="P68" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q68" s="61"/>
+      <c r="R68" s="61"/>
+      <c r="S68" s="61"/>
+    </row>
+    <row r="69" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" s="58"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="54">
+        <v>16000</v>
+      </c>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54">
+        <v>22700</v>
+      </c>
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
+      <c r="L69" s="62">
+        <f t="shared" si="4"/>
+        <v>-6700</v>
+      </c>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="60"/>
+    </row>
+    <row r="70" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="54">
+        <v>17000</v>
+      </c>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="54">
+        <v>2800</v>
+      </c>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="L70" s="62">
+        <f t="shared" si="4"/>
+        <v>14200</v>
+      </c>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="63"/>
+      <c r="P70" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q70" s="61"/>
+      <c r="R70" s="61"/>
+      <c r="S70" s="61"/>
+    </row>
+    <row r="71" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="58"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="54">
+        <v>18000</v>
+      </c>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
+      <c r="H71" s="54">
+        <v>2900</v>
+      </c>
+      <c r="I71" s="54"/>
+      <c r="J71" s="54"/>
+      <c r="K71" s="54"/>
+      <c r="L71" s="62">
+        <f t="shared" si="4"/>
+        <v>15100</v>
+      </c>
+      <c r="M71" s="63"/>
+      <c r="N71" s="63"/>
+      <c r="O71" s="63"/>
+      <c r="P71" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q71" s="61"/>
+      <c r="R71" s="61"/>
+      <c r="S71" s="61"/>
+    </row>
+    <row r="72" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53"/>
+      <c r="M72" s="53"/>
+      <c r="N72" s="53"/>
+      <c r="O72" s="53"/>
+    </row>
+    <row r="73" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" s="66"/>
+      <c r="C73" s="66">
+        <f>COUNTA(A54:D71)</f>
+        <v>18</v>
+      </c>
+      <c r="D73" s="66"/>
+      <c r="E73" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="F73" s="70">
+        <f>SUM(E54:G71)</f>
+        <v>171000</v>
+      </c>
+      <c r="G73" s="67"/>
+      <c r="H73" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="I73" s="68"/>
+      <c r="J73" s="69">
+        <f>SUM(H54:K71)</f>
+        <v>116900</v>
+      </c>
+      <c r="K73" s="68"/>
+      <c r="L73" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="M73" s="55"/>
+      <c r="N73" s="71">
+        <f>F73-J73</f>
+        <v>54100</v>
+      </c>
+      <c r="O73" s="55"/>
+      <c r="P73" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q73" s="55"/>
+      <c r="R73" s="71" t="str">
+        <f>IF(N73&gt;=50000,"Good","Bad")</f>
+        <v>Good</v>
+      </c>
+      <c r="S73" s="55"/>
+    </row>
+    <row r="74" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="66"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="67"/>
+      <c r="F74" s="67"/>
+      <c r="G74" s="67"/>
+      <c r="H74" s="68"/>
+      <c r="I74" s="68"/>
+      <c r="J74" s="68"/>
+      <c r="K74" s="68"/>
+      <c r="L74" s="55"/>
+      <c r="M74" s="55"/>
+      <c r="N74" s="55"/>
+      <c r="O74" s="55"/>
+      <c r="P74" s="55"/>
+      <c r="Q74" s="55"/>
+      <c r="R74" s="55"/>
+      <c r="S74" s="55"/>
+    </row>
+    <row r="75" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+    </row>
+    <row r="79" spans="1:19" ht="32" x14ac:dyDescent="0.4">
+      <c r="I79" s="51"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A52:S71" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
+    <filterColumn colId="0" showButton="0"/>
+    <filterColumn colId="1" showButton="0"/>
+    <filterColumn colId="2" showButton="0"/>
+    <filterColumn colId="4" showButton="0"/>
+    <filterColumn colId="5" showButton="0"/>
+    <filterColumn colId="7" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="9" showButton="0"/>
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="12" showButton="0"/>
+    <filterColumn colId="13" showButton="0"/>
+    <filterColumn colId="15" showButton="0"/>
+    <filterColumn colId="16" showButton="0"/>
+    <filterColumn colId="17" showButton="0"/>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K15">
     <sortCondition ref="A4:A15"/>
     <sortCondition ref="B4:B15"/>
     <sortCondition ref="C4:C15"/>
     <sortCondition ref="I4:I15"/>
   </sortState>
-  <mergeCells count="6">
+  <mergeCells count="116">
+    <mergeCell ref="P73:Q74"/>
+    <mergeCell ref="A47:S49"/>
+    <mergeCell ref="R73:S74"/>
+    <mergeCell ref="L66:O66"/>
+    <mergeCell ref="L67:O67"/>
+    <mergeCell ref="L68:O68"/>
+    <mergeCell ref="L69:O69"/>
+    <mergeCell ref="L70:O70"/>
+    <mergeCell ref="L52:O53"/>
+    <mergeCell ref="L54:O54"/>
+    <mergeCell ref="L55:O55"/>
+    <mergeCell ref="L56:O56"/>
+    <mergeCell ref="L57:O57"/>
+    <mergeCell ref="L58:O58"/>
+    <mergeCell ref="L59:O59"/>
+    <mergeCell ref="L60:O60"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="L62:O62"/>
+    <mergeCell ref="L63:O63"/>
+    <mergeCell ref="L64:O64"/>
+    <mergeCell ref="L65:O65"/>
+    <mergeCell ref="N73:O74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:G74"/>
+    <mergeCell ref="H73:I74"/>
+    <mergeCell ref="J73:K74"/>
+    <mergeCell ref="L73:M74"/>
+    <mergeCell ref="P68:S68"/>
+    <mergeCell ref="P69:S69"/>
+    <mergeCell ref="P70:S70"/>
+    <mergeCell ref="P71:S71"/>
+    <mergeCell ref="L72:O72"/>
+    <mergeCell ref="L71:O71"/>
+    <mergeCell ref="P63:S63"/>
+    <mergeCell ref="P64:S64"/>
+    <mergeCell ref="P65:S65"/>
+    <mergeCell ref="P66:S66"/>
+    <mergeCell ref="P67:S67"/>
+    <mergeCell ref="P58:S58"/>
+    <mergeCell ref="P59:S59"/>
+    <mergeCell ref="P60:S60"/>
+    <mergeCell ref="P61:S61"/>
+    <mergeCell ref="P62:S62"/>
+    <mergeCell ref="H67:K67"/>
+    <mergeCell ref="H68:K68"/>
+    <mergeCell ref="H69:K69"/>
+    <mergeCell ref="H70:K70"/>
+    <mergeCell ref="H71:K71"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H57:K57"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="H64:K64"/>
+    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="H72:K72"/>
+    <mergeCell ref="A73:B74"/>
+    <mergeCell ref="C73:D74"/>
+    <mergeCell ref="A52:D53"/>
+    <mergeCell ref="E52:G53"/>
+    <mergeCell ref="H52:K53"/>
+    <mergeCell ref="P52:S53"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="P57:S57"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="P54:S54"/>
+    <mergeCell ref="P55:S55"/>
+    <mergeCell ref="P56:S56"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:K1"/>
@@ -7968,7 +9322,19 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="I3:I15">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7980,19 +9346,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K15">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="uniqueValues" dxfId="5" priority="6"/>
+    <cfRule type="uniqueValues" dxfId="23" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB3:AB14">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB8">
-    <cfRule type="uniqueValues" dxfId="3" priority="2"/>
+    <cfRule type="uniqueValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="D3:D15">
+    <cfRule type="iconSet" priority="13">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8001,6 +9374,92 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P54:S71">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",P54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="iconSet" priority="11">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H54:K71">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E54:G71">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L54:O71">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/eXCEL.xlsx
+++ b/eXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2AC8A7-D47C-8B48-AA27-2040460B41CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB274DC-8E8F-DF43-8E8B-52C179703550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14020" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$52:$S$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$52:$AN$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="8" r:id="rId5"/>
+    <pivotCache cacheId="9" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="140">
   <si>
     <t>Sno</t>
   </si>
@@ -301,9 +301,6 @@
     <t>Expence_Name</t>
   </si>
   <si>
-    <t>Costing</t>
-  </si>
-  <si>
     <t>Budget</t>
   </si>
   <si>
@@ -382,13 +379,112 @@
     <t>Balance</t>
   </si>
   <si>
-    <t>DASH_BOARD 101(Expence Tracker)</t>
-  </si>
-  <si>
     <t>Remarks:</t>
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>Percentage of Budget used:</t>
+  </si>
+  <si>
+    <t>Percentage Saved:</t>
+  </si>
+  <si>
+    <t>Expence</t>
+  </si>
+  <si>
+    <t>DASH_BOARD_1(Expence Tracker)</t>
+  </si>
+  <si>
+    <t>DASH_BOARD-2(Sales Tracker)</t>
+  </si>
+  <si>
+    <t>Product_1</t>
+  </si>
+  <si>
+    <t>Product_2</t>
+  </si>
+  <si>
+    <t>Product_3</t>
+  </si>
+  <si>
+    <t>Product_4</t>
+  </si>
+  <si>
+    <t>Product_5</t>
+  </si>
+  <si>
+    <t>Product_6</t>
+  </si>
+  <si>
+    <t>Product_7</t>
+  </si>
+  <si>
+    <t>Product_8</t>
+  </si>
+  <si>
+    <t>Product_9</t>
+  </si>
+  <si>
+    <t>Product_10</t>
+  </si>
+  <si>
+    <t>Product_11</t>
+  </si>
+  <si>
+    <t>Product_12</t>
+  </si>
+  <si>
+    <t>Product_13</t>
+  </si>
+  <si>
+    <t>Product_14</t>
+  </si>
+  <si>
+    <t>Product_15</t>
+  </si>
+  <si>
+    <t>Product_16</t>
+  </si>
+  <si>
+    <t>Product_17</t>
+  </si>
+  <si>
+    <t>Product_18</t>
+  </si>
+  <si>
+    <t>Product_Name</t>
+  </si>
+  <si>
+    <t>Cost of Product</t>
+  </si>
+  <si>
+    <t>Units_Sold</t>
+  </si>
+  <si>
+    <t>MRP</t>
+  </si>
+  <si>
+    <t>Profit/Loss</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Total_Units_Sold:</t>
+  </si>
+  <si>
+    <t>Profit/Loss:</t>
+  </si>
+  <si>
+    <t>Percentage of Profit:</t>
+  </si>
+  <si>
+    <t>Most_Selling</t>
+  </si>
+  <si>
+    <t>Max_Profit:</t>
   </si>
 </sst>
 </file>
@@ -397,7 +493,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -578,12 +674,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -594,8 +684,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -749,12 +845,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -839,6 +944,102 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -857,62 +1058,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -920,7 +1069,167 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
@@ -1161,13 +1470,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1183,134 +1485,11 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2752,7 +2931,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$AA$2</c:f>
+              <c:f>Sheet1!$AB$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3215,7 +3394,7 @@
           </c:dPt>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$14</c:f>
+              <c:f>Sheet1!$AB$3:$AB$14</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3269,7 +3448,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$AB$2</c:f>
+              <c:f>Sheet1!$AC$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3730,7 +3909,7 @@
           </c:dPt>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$14</c:f>
+              <c:f>Sheet1!$AC$3:$AC$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -3851,6 +4030,2617 @@
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Budget Vs Cost</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0580927384076984E-2"/>
+          <c:y val="0.1439122193059201"/>
+          <c:w val="0.86497462817147852"/>
+          <c:h val="0.54419655876348794"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$52:$E$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>18000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$52:$F$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent3">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$52:$G$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$52:$H$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>22100</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>22300</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>22400</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>22700</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2800</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="&quot;₹&quot;#,##0.00">
+                  <c:v>2900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent5">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$52:$I$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$52:$J$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$52:$K$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2501-7A48-B348-21C43FF8BD53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="273510912"/>
+        <c:axId val="293715744"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="273510912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="293715744"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="293715744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="273510912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Budget</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>vs</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cost</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>j</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-045B-4045-B791-49613F2D161A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-045B-4045-B791-49613F2D161A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>(Sheet1!$F$73,Sheet1!$J$73)</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"#,##0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>116900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2577-B442-86DA-C071B93570F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.72559265516911597"/>
+          <c:y val="0.41131089209481253"/>
+          <c:w val="0.27278791163250343"/>
+          <c:h val="0.29061053739447207"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AB$73</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total_Cost:</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-2857-0347-A2BC-954BB0999BA1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AC$73:$AI$73</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"#,##0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="1">
+                  <c:v>171000</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CAFF-0547-86BA-F10CD8630ED3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AB$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000F-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000011-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000013-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000015-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000017-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="5"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000019-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="6"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000001B-2857-0347-A2BC-954BB0999BA1}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AC$74:$AI$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="7"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-CAFF-0547-86BA-F10CD8630ED3}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16935870516185478"/>
+          <c:y val="0.19483814523184603"/>
+          <c:w val="0.78230796150481186"/>
+          <c:h val="0.72128098571011956"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AC$52</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MRP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$Z$53:$Z$71</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"#,##0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AC$53:$AC$71</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"#,##0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3200</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11200</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13200</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15200</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16200</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17200</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BD1D-ED46-916A-19A11F8DA363}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="192586080"/>
+        <c:axId val="141474784"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AA$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Z$53:$Z$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AA$53:$AA$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-BD1D-ED46-916A-19A11F8DA363}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AB$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Z$53:$Z$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AB$53:$AB$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-BD1D-ED46-916A-19A11F8DA363}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AD$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Z$53:$Z$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AD$53:$AD$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-BD1D-ED46-916A-19A11F8DA363}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AE$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent5"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Z$53:$Z$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AE$53:$AE$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-BD1D-ED46-916A-19A11F8DA363}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AF$52</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent6"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Z$53:$Z$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AF$53:$AF$71</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>"₹"#,##0.00</c:formatCode>
+                      <c:ptCount val="19"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-BD1D-ED46-916A-19A11F8DA363}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="192586080"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141474784"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141474784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="192586080"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -4034,6 +6824,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -6086,6 +9036,2180 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -6213,7 +11337,7 @@
       <xdr:rowOff>117365</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>534276</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>174588</xdr:rowOff>
@@ -6236,6 +11360,150 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>793750</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>78316</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>423333</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21061AE1-7322-94EE-81DB-0AA4EE7C1794}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>645583</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>43038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>7055</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>155222</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F15CA261-CCFB-6B54-C8A3-3DF31FDB252F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>802410</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>158172</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>750455</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>86591</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90632CF7-4AFA-984E-74B8-FED4F147FBA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>51953</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>187034</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>634999</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>57726</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18ECB44C-99D3-C9C0-0980-13742B93FFBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6270,7 +11538,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="APPLE" refreshedDate="46229.788862152775" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{1E6120FD-99F1-3C46-9449-0A4C2058F4E5}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="AA2:AB14" sheet="Sheet1"/>
+    <worksheetSource ref="AB2:AC14" sheet="Sheet1"/>
   </cacheSource>
   <cacheFields count="2">
     <cacheField name="Avg Sal" numFmtId="2">
@@ -6591,7 +11859,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" numFmtId="2" showAll="0">
@@ -6706,7 +11974,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -6747,27 +12015,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A2:L15" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="doj" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="doj" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="20">
       <calculatedColumnFormula>SUM(F3+G3+H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="3">
+    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="19">
       <calculatedColumnFormula>AVERAGE(F3:H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="2">
+    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="18">
       <calculatedColumnFormula>CONCATENATE(B3,"  ",C3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="1">
+    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="17">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6798,7 +12066,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}" name="Table5" displayName="Table5" ref="M4:P9" totalsRowShown="0" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}" name="Table5" displayName="Table5" ref="M4:P9" totalsRowShown="0" tableBorderDxfId="16">
   <autoFilter ref="M4:P9" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2E8124BF-9EED-0049-9B4E-570F10E09411}" name="Column1"/>
@@ -7281,7 +12549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
-  <dimension ref="A1:AE79"/>
+  <dimension ref="A1:AN79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="28.1640625" customWidth="1"/>
@@ -7290,30 +12558,34 @@
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.33203125" customWidth="1"/>
+    <col min="27" max="27" width="14.1640625" customWidth="1"/>
+    <col min="31" max="31" width="22.5" customWidth="1"/>
+    <col min="35" max="35" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:32" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="Y1" s="3" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="Z1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:32" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="26" t="s">
         <v>58</v>
       </c>
@@ -7361,18 +12633,18 @@
       </c>
       <c r="V2" s="8"/>
       <c r="W2" s="9"/>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AC2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
     </row>
-    <row r="3" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
@@ -7382,7 +12654,7 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="44" t="s">
         <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -7416,19 +12688,19 @@
       <c r="S3" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="6">
-        <f t="shared" ref="AA3:AA14" si="0">AVERAGE(F4:H4)</f>
+      <c r="AB3" s="6">
+        <f t="shared" ref="AB3:AB14" si="0">AVERAGE(F4:H4)</f>
         <v>1500</v>
       </c>
-      <c r="AB3" s="1" t="str">
-        <f>CONCATENATE(B4,"  ",C4)</f>
+      <c r="AC3" s="1" t="str">
+        <f t="shared" ref="AC3:AC14" si="1">CONCATENATE(B4,"  ",C4)</f>
         <v>A  X</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17">
         <v>1</v>
       </c>
@@ -7454,7 +12726,7 @@
         <v>1500</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" ref="I4:I15" si="1">SUM(F4+G4+H4)</f>
+        <f t="shared" ref="I4:I15" si="2">SUM(F4+G4+H4)</f>
         <v>4500</v>
       </c>
       <c r="J4" s="6">
@@ -7462,7 +12734,7 @@
         <v>1500</v>
       </c>
       <c r="K4" s="19" t="str">
-        <f>CONCATENATE(B4,"  ",C4)</f>
+        <f t="shared" ref="K4:K15" si="3">CONCATENATE(B4,"  ",C4)</f>
         <v>A  X</v>
       </c>
       <c r="L4" s="40" t="str">
@@ -7493,19 +12765,19 @@
       <c r="V4" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AB4" s="6">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="AB4" s="1" t="str">
-        <f>CONCATENATE(B5,"  ",C5)</f>
+      <c r="AC4" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>ghg  hg</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17">
         <v>2</v>
       </c>
@@ -7531,15 +12803,15 @@
         <v>1600</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4800</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" ref="J5:J15" si="2">AVERAGE(F5:H5)</f>
+        <f t="shared" ref="J5:J15" si="4">AVERAGE(F5:H5)</f>
         <v>1600</v>
       </c>
       <c r="K5" s="19" t="str">
-        <f>CONCATENATE(B5,"  ",C5)</f>
+        <f t="shared" si="3"/>
         <v>ghg  hg</v>
       </c>
       <c r="L5" s="40" t="str">
@@ -7573,19 +12845,19 @@
       <c r="V5" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AB5" s="6">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="AB5" s="1" t="str">
-        <f>CONCATENATE(B6,"  ",C6)</f>
+      <c r="AC5" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>A  X</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17">
         <v>3</v>
       </c>
@@ -7611,15 +12883,15 @@
         <v>1700</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5100</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1700</v>
       </c>
       <c r="K6" s="19" t="str">
-        <f>CONCATENATE(B6,"  ",C6)</f>
+        <f t="shared" si="3"/>
         <v>A  X</v>
       </c>
       <c r="L6" s="40" t="str">
@@ -7653,19 +12925,19 @@
       <c r="V6" t="s">
         <v>44</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AB6" s="6">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="AB6" s="1" t="str">
-        <f>CONCATENATE(B7,"  ",C7)</f>
+      <c r="AC6" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>B  Y</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17">
         <v>4</v>
       </c>
@@ -7691,15 +12963,15 @@
         <v>1800</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1800</v>
       </c>
       <c r="K7" s="19" t="str">
-        <f>CONCATENATE(B7,"  ",C7)</f>
+        <f t="shared" si="3"/>
         <v>B  Y</v>
       </c>
       <c r="L7" s="40" t="str">
@@ -7733,19 +13005,19 @@
       <c r="V7" t="s">
         <v>44</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AB7" s="6">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="AB7" s="1" t="str">
-        <f>CONCATENATE(B8,"  ",C8)</f>
+      <c r="AC7" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>ghg  hggh</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17">
         <v>5</v>
       </c>
@@ -7771,15 +13043,15 @@
         <v>1900</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5700</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1900</v>
       </c>
       <c r="K8" s="19" t="str">
-        <f>CONCATENATE(B8,"  ",C8)</f>
+        <f t="shared" si="3"/>
         <v>ghg  hggh</v>
       </c>
       <c r="L8" s="40" t="str">
@@ -7813,19 +13085,19 @@
       <c r="V8" t="s">
         <v>44</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AB8" s="6">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="AB8" s="1" t="str">
-        <f>CONCATENATE(B9,"  ",C9)</f>
+      <c r="AC8" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>c  v</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>6</v>
       </c>
@@ -7851,15 +13123,15 @@
         <v>2000</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6000</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2000</v>
       </c>
       <c r="K9" s="20" t="str">
-        <f>CONCATENATE(B9,"  ",C9)</f>
+        <f t="shared" si="3"/>
         <v>c  v</v>
       </c>
       <c r="L9" s="40" t="str">
@@ -7893,19 +13165,19 @@
       <c r="V9" t="s">
         <v>44</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AB9" s="6">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="AB9" s="1" t="str">
-        <f>CONCATENATE(B10,"  ",C10)</f>
+      <c r="AC9" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>A  X</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17">
         <v>7</v>
       </c>
@@ -7931,15 +13203,15 @@
         <v>2100</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6300</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2100</v>
       </c>
       <c r="K10" s="19" t="str">
-        <f>CONCATENATE(B10,"  ",C10)</f>
+        <f t="shared" si="3"/>
         <v>A  X</v>
       </c>
       <c r="L10" s="6" t="str">
@@ -7958,19 +13230,19 @@
       <c r="V10" t="s">
         <v>44</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AB10" s="6">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="AB10" s="1" t="str">
-        <f>CONCATENATE(B11,"  ",C11)</f>
+      <c r="AC10" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>k  Y</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17">
         <v>8</v>
       </c>
@@ -7996,15 +13268,15 @@
         <v>2200</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6600</v>
       </c>
       <c r="J11" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2200</v>
       </c>
       <c r="K11" s="19" t="str">
-        <f>CONCATENATE(B11,"  ",C11)</f>
+        <f t="shared" si="3"/>
         <v>k  Y</v>
       </c>
       <c r="L11" s="6" t="str">
@@ -8023,19 +13295,19 @@
       <c r="V11" t="s">
         <v>44</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AA11" s="6">
+      <c r="AB11" s="6">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="AB11" s="1" t="str">
-        <f>CONCATENATE(B12,"  ",C12)</f>
+      <c r="AC11" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>A  X</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <v>9</v>
       </c>
@@ -8061,15 +13333,15 @@
         <v>2300</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6900</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2300</v>
       </c>
       <c r="K12" s="19" t="str">
-        <f>CONCATENATE(B12,"  ",C12)</f>
+        <f t="shared" si="3"/>
         <v>A  X</v>
       </c>
       <c r="L12" s="6" t="str">
@@ -8088,19 +13360,19 @@
       <c r="V12" t="s">
         <v>44</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="6">
+      <c r="AB12" s="6">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
-      <c r="AB12" s="1" t="str">
-        <f>CONCATENATE(B13,"  ",C13)</f>
+      <c r="AC12" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>B  Y</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <v>10</v>
       </c>
@@ -8126,34 +13398,34 @@
         <v>2400</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7200</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2400</v>
       </c>
       <c r="K13" s="19" t="str">
-        <f>CONCATENATE(B13,"  ",C13)</f>
+        <f t="shared" si="3"/>
         <v>B  Y</v>
       </c>
       <c r="L13" s="6" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AA13" s="6">
+      <c r="AB13" s="6">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="AB13" s="1" t="str">
-        <f>CONCATENATE(B14,"  ",C14)</f>
+      <c r="AC13" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>A  X</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17">
         <v>11</v>
       </c>
@@ -8179,31 +13451,31 @@
         <v>2500</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7500</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2500</v>
       </c>
       <c r="K14" s="19" t="str">
-        <f>CONCATENATE(B14,"  ",C14)</f>
+        <f t="shared" si="3"/>
         <v>A  X</v>
       </c>
       <c r="L14" s="6" t="str">
         <f>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</f>
         <v>Good</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AB14" s="6">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
-      <c r="AB14" s="1" t="str">
-        <f>CONCATENATE(B15,"  ",C15)</f>
+      <c r="AC14" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>B  Y</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21">
         <v>12</v>
       </c>
@@ -8229,15 +13501,15 @@
         <v>2600</v>
       </c>
       <c r="I15" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7800</v>
       </c>
       <c r="J15" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2600</v>
       </c>
       <c r="K15" s="25" t="str">
-        <f>CONCATENATE(B15,"  ",C15)</f>
+        <f t="shared" si="3"/>
         <v>B  Y</v>
       </c>
       <c r="L15" s="24" t="str">
@@ -8245,21 +13517,21 @@
         <v>Good</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E16" s="48" t="s">
+    <row r="16" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="48"/>
+      <c r="F16" s="84"/>
       <c r="G16" s="12">
-        <f t="shared" ref="G16:I16" si="3">SUM(G4:G15)</f>
+        <f t="shared" ref="G16:I16" si="5">SUM(G4:G15)</f>
         <v>24600</v>
       </c>
       <c r="H16" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24600</v>
       </c>
       <c r="I16" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>73800</v>
       </c>
       <c r="J16" s="12">
@@ -8268,10 +13540,10 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E17" s="49" t="s">
+      <c r="E17" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="49"/>
+      <c r="F17" s="85"/>
       <c r="G17" s="15">
         <f>+COUNT(G4:G15)</f>
         <v>12</v>
@@ -8321,21 +13593,21 @@
       <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
     </row>
     <row r="22" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="39"/>
@@ -8351,15 +13623,15 @@
       <c r="K22" s="38"/>
     </row>
     <row r="23" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="82"/>
     </row>
     <row r="24" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -8374,813 +13646,1683 @@
     <row r="30" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="65" t="s">
+    <row r="33" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="77"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="77"/>
+      <c r="O47" s="77"/>
+      <c r="P47" s="77"/>
+      <c r="Q47" s="77"/>
+      <c r="R47" s="77"/>
+      <c r="S47" s="77"/>
+      <c r="U47" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="V47" s="77"/>
+      <c r="W47" s="77"/>
+      <c r="X47" s="77"/>
+      <c r="Y47" s="77"/>
+      <c r="Z47" s="77"/>
+      <c r="AA47" s="77"/>
+      <c r="AB47" s="77"/>
+      <c r="AC47" s="77"/>
+      <c r="AD47" s="77"/>
+      <c r="AE47" s="77"/>
+      <c r="AF47" s="77"/>
+      <c r="AG47" s="77"/>
+      <c r="AH47" s="77"/>
+      <c r="AI47" s="77"/>
+      <c r="AJ47" s="77"/>
+      <c r="AK47" s="77"/>
+      <c r="AL47" s="77"/>
+      <c r="AM47" s="77"/>
+      <c r="AN47" s="77"/>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
+      <c r="I48" s="77"/>
+      <c r="J48" s="77"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="77"/>
+      <c r="M48" s="77"/>
+      <c r="N48" s="77"/>
+      <c r="O48" s="77"/>
+      <c r="P48" s="77"/>
+      <c r="Q48" s="77"/>
+      <c r="R48" s="77"/>
+      <c r="S48" s="77"/>
+      <c r="U48" s="77"/>
+      <c r="V48" s="77"/>
+      <c r="W48" s="77"/>
+      <c r="X48" s="77"/>
+      <c r="Y48" s="77"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+      <c r="AC48" s="77"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="77"/>
+      <c r="AF48" s="77"/>
+      <c r="AG48" s="77"/>
+      <c r="AH48" s="77"/>
+      <c r="AI48" s="77"/>
+      <c r="AJ48" s="77"/>
+      <c r="AK48" s="77"/>
+      <c r="AL48" s="77"/>
+      <c r="AM48" s="77"/>
+      <c r="AN48" s="77"/>
+    </row>
+    <row r="49" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
+      <c r="I49" s="77"/>
+      <c r="J49" s="77"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="77"/>
+      <c r="M49" s="77"/>
+      <c r="N49" s="77"/>
+      <c r="O49" s="77"/>
+      <c r="P49" s="77"/>
+      <c r="Q49" s="77"/>
+      <c r="R49" s="77"/>
+      <c r="S49" s="77"/>
+      <c r="U49" s="77"/>
+      <c r="V49" s="77"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="77"/>
+      <c r="Y49" s="77"/>
+      <c r="Z49" s="77"/>
+      <c r="AA49" s="77"/>
+      <c r="AB49" s="77"/>
+      <c r="AC49" s="77"/>
+      <c r="AD49" s="77"/>
+      <c r="AE49" s="77"/>
+      <c r="AF49" s="77"/>
+      <c r="AG49" s="77"/>
+      <c r="AH49" s="77"/>
+      <c r="AI49" s="77"/>
+      <c r="AJ49" s="77"/>
+      <c r="AK49" s="77"/>
+      <c r="AL49" s="77"/>
+      <c r="AM49" s="77"/>
+      <c r="AN49" s="77"/>
+    </row>
+    <row r="52" spans="1:40" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="78"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78" t="s">
+        <v>108</v>
+      </c>
+      <c r="I52" s="78"/>
+      <c r="J52" s="78"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="M52" s="78"/>
+      <c r="N52" s="78"/>
+      <c r="O52" s="78"/>
+      <c r="P52" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="65"/>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
-      <c r="N47" s="65"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="65"/>
-      <c r="Q47" s="65"/>
-      <c r="R47" s="65"/>
-      <c r="S47" s="65"/>
+      <c r="Q52" s="78"/>
+      <c r="R52" s="78"/>
+      <c r="S52" s="78"/>
+      <c r="U52" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="V52" s="78"/>
+      <c r="W52" s="78"/>
+      <c r="X52" s="78"/>
+      <c r="Y52" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z52" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA52" s="78"/>
+      <c r="AB52" s="78"/>
+      <c r="AC52" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD52" s="78"/>
+      <c r="AE52" s="78"/>
+      <c r="AF52" s="78"/>
+      <c r="AG52" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH52" s="78"/>
+      <c r="AI52" s="78"/>
+      <c r="AJ52" s="78"/>
+      <c r="AK52" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL52" s="78"/>
+      <c r="AM52" s="78"/>
+      <c r="AN52" s="78"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65"/>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
-      <c r="N48" s="65"/>
-      <c r="O48" s="65"/>
-      <c r="P48" s="65"/>
-      <c r="Q48" s="65"/>
-      <c r="R48" s="65"/>
-      <c r="S48" s="65"/>
+    <row r="53" spans="1:40" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="78"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="78"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="78"/>
+      <c r="F53" s="78"/>
+      <c r="G53" s="78"/>
+      <c r="H53" s="78"/>
+      <c r="I53" s="78"/>
+      <c r="J53" s="78"/>
+      <c r="K53" s="78"/>
+      <c r="L53" s="78"/>
+      <c r="M53" s="78"/>
+      <c r="N53" s="78"/>
+      <c r="O53" s="78"/>
+      <c r="P53" s="78"/>
+      <c r="Q53" s="78"/>
+      <c r="R53" s="78"/>
+      <c r="S53" s="78"/>
+      <c r="U53" s="78"/>
+      <c r="V53" s="78"/>
+      <c r="W53" s="78"/>
+      <c r="X53" s="78"/>
+      <c r="Y53" s="56"/>
+      <c r="Z53" s="78"/>
+      <c r="AA53" s="78"/>
+      <c r="AB53" s="78"/>
+      <c r="AC53" s="78"/>
+      <c r="AD53" s="78"/>
+      <c r="AE53" s="78"/>
+      <c r="AF53" s="78"/>
+      <c r="AG53" s="78"/>
+      <c r="AH53" s="78"/>
+      <c r="AI53" s="78"/>
+      <c r="AJ53" s="78"/>
+      <c r="AK53" s="78"/>
+      <c r="AL53" s="78"/>
+      <c r="AM53" s="78"/>
+      <c r="AN53" s="78"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A49" s="65"/>
-      <c r="B49" s="65"/>
-      <c r="C49" s="65"/>
-      <c r="D49" s="65"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="65"/>
-      <c r="O49" s="65"/>
-      <c r="P49" s="65"/>
-      <c r="Q49" s="65"/>
-      <c r="R49" s="65"/>
-      <c r="S49" s="65"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A52" s="56" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="56"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56" t="s">
+    <row r="54" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="I52" s="56"/>
-      <c r="J52" s="56"/>
-      <c r="K52" s="56"/>
-      <c r="L52" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="M52" s="56"/>
-      <c r="N52" s="56"/>
-      <c r="O52" s="56"/>
-      <c r="P52" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q52" s="56"/>
-      <c r="R52" s="56"/>
-      <c r="S52" s="56"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A53" s="56"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="56"/>
-      <c r="M53" s="56"/>
-      <c r="N53" s="56"/>
-      <c r="O53" s="56"/>
-      <c r="P53" s="56"/>
-      <c r="Q53" s="56"/>
-      <c r="R53" s="56"/>
-      <c r="S53" s="56"/>
-    </row>
-    <row r="54" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A54" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="54">
+      <c r="B54" s="68"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="70">
         <v>1000</v>
       </c>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="64">
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="86">
         <v>1200</v>
       </c>
-      <c r="I54" s="64"/>
-      <c r="J54" s="64"/>
-      <c r="K54" s="64"/>
-      <c r="L54" s="62">
+      <c r="I54" s="86"/>
+      <c r="J54" s="86"/>
+      <c r="K54" s="86"/>
+      <c r="L54" s="71">
         <f>E54-H54</f>
         <v>-200</v>
       </c>
-      <c r="M54" s="63"/>
-      <c r="N54" s="63"/>
-      <c r="O54" s="63"/>
-      <c r="P54" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q54" s="60"/>
-      <c r="R54" s="60"/>
-      <c r="S54" s="60"/>
+      <c r="M54" s="72"/>
+      <c r="N54" s="72"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q54" s="79"/>
+      <c r="R54" s="79"/>
+      <c r="S54" s="79"/>
+      <c r="U54" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="V54" s="68"/>
+      <c r="W54" s="68"/>
+      <c r="X54" s="69"/>
+      <c r="Y54" s="47">
+        <v>1000</v>
+      </c>
+      <c r="Z54" s="70">
+        <v>1000</v>
+      </c>
+      <c r="AA54" s="70"/>
+      <c r="AB54" s="70"/>
+      <c r="AC54" s="70">
+        <v>1000</v>
+      </c>
+      <c r="AD54" s="70"/>
+      <c r="AE54" s="70"/>
+      <c r="AF54" s="70"/>
+      <c r="AG54" s="71">
+        <f>AC54-Z54</f>
+        <v>0</v>
+      </c>
+      <c r="AH54" s="72"/>
+      <c r="AI54" s="72"/>
+      <c r="AJ54" s="72"/>
+      <c r="AK54" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL54" s="79"/>
+      <c r="AM54" s="79"/>
+      <c r="AN54" s="79"/>
     </row>
-    <row r="55" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A55" s="57" t="s">
+    <row r="55" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="70">
+        <v>2000</v>
+      </c>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70">
+        <v>1300</v>
+      </c>
+      <c r="I55" s="70"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="71">
+        <f t="shared" ref="L55:L71" si="6">E55-H55</f>
+        <v>700</v>
+      </c>
+      <c r="M55" s="72"/>
+      <c r="N55" s="72"/>
+      <c r="O55" s="72"/>
+      <c r="P55" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q55" s="73"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="73"/>
+      <c r="U55" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="V55" s="68"/>
+      <c r="W55" s="68"/>
+      <c r="X55" s="69"/>
+      <c r="Y55" s="47">
+        <v>2000</v>
+      </c>
+      <c r="Z55" s="70">
+        <v>2000</v>
+      </c>
+      <c r="AA55" s="70"/>
+      <c r="AB55" s="70"/>
+      <c r="AC55" s="57">
+        <v>2200</v>
+      </c>
+      <c r="AD55" s="58"/>
+      <c r="AE55" s="58"/>
+      <c r="AF55" s="59"/>
+      <c r="AG55" s="71">
+        <f t="shared" ref="AG55:AG71" si="7">AC55-Z55</f>
+        <v>200</v>
+      </c>
+      <c r="AH55" s="72"/>
+      <c r="AI55" s="72"/>
+      <c r="AJ55" s="72"/>
+      <c r="AK55" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL55" s="73"/>
+      <c r="AM55" s="73"/>
+      <c r="AN55" s="73"/>
+    </row>
+    <row r="56" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="54">
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="70">
+        <v>3000</v>
+      </c>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70">
+        <v>1400</v>
+      </c>
+      <c r="I56" s="70"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="71">
+        <f t="shared" si="6"/>
+        <v>1600</v>
+      </c>
+      <c r="M56" s="72"/>
+      <c r="N56" s="72"/>
+      <c r="O56" s="72"/>
+      <c r="P56" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q56" s="73"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="73"/>
+      <c r="U56" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="V56" s="68"/>
+      <c r="W56" s="68"/>
+      <c r="X56" s="69"/>
+      <c r="Y56" s="47">
+        <v>3000</v>
+      </c>
+      <c r="Z56" s="70">
+        <v>3000</v>
+      </c>
+      <c r="AA56" s="70"/>
+      <c r="AB56" s="70"/>
+      <c r="AC56" s="70">
+        <v>3200</v>
+      </c>
+      <c r="AD56" s="70"/>
+      <c r="AE56" s="70"/>
+      <c r="AF56" s="70"/>
+      <c r="AG56" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH56" s="72"/>
+      <c r="AI56" s="72"/>
+      <c r="AJ56" s="72"/>
+      <c r="AK56" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL56" s="73"/>
+      <c r="AM56" s="73"/>
+      <c r="AN56" s="73"/>
+    </row>
+    <row r="57" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="70">
+        <v>4000</v>
+      </c>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70">
+        <v>1500</v>
+      </c>
+      <c r="I57" s="70"/>
+      <c r="J57" s="70"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="71">
+        <f t="shared" si="6"/>
+        <v>2500</v>
+      </c>
+      <c r="M57" s="72"/>
+      <c r="N57" s="72"/>
+      <c r="O57" s="72"/>
+      <c r="P57" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q57" s="73"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="73"/>
+      <c r="U57" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="V57" s="68"/>
+      <c r="W57" s="68"/>
+      <c r="X57" s="69"/>
+      <c r="Y57" s="47">
+        <v>4000</v>
+      </c>
+      <c r="Z57" s="70">
+        <v>4000</v>
+      </c>
+      <c r="AA57" s="70"/>
+      <c r="AB57" s="70"/>
+      <c r="AC57" s="70">
+        <v>4200</v>
+      </c>
+      <c r="AD57" s="70"/>
+      <c r="AE57" s="70"/>
+      <c r="AF57" s="70"/>
+      <c r="AG57" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH57" s="72"/>
+      <c r="AI57" s="72"/>
+      <c r="AJ57" s="72"/>
+      <c r="AK57" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL57" s="73"/>
+      <c r="AM57" s="73"/>
+      <c r="AN57" s="73"/>
+    </row>
+    <row r="58" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="70">
+        <v>5000</v>
+      </c>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="70">
+        <v>1600</v>
+      </c>
+      <c r="I58" s="70"/>
+      <c r="J58" s="70"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="71">
+        <f t="shared" si="6"/>
+        <v>3400</v>
+      </c>
+      <c r="M58" s="72"/>
+      <c r="N58" s="72"/>
+      <c r="O58" s="72"/>
+      <c r="P58" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q58" s="73"/>
+      <c r="R58" s="73"/>
+      <c r="S58" s="73"/>
+      <c r="U58" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="V58" s="68"/>
+      <c r="W58" s="68"/>
+      <c r="X58" s="69"/>
+      <c r="Y58" s="47">
+        <v>5000</v>
+      </c>
+      <c r="Z58" s="70">
+        <v>5000</v>
+      </c>
+      <c r="AA58" s="70"/>
+      <c r="AB58" s="70"/>
+      <c r="AC58" s="57">
+        <v>5200</v>
+      </c>
+      <c r="AD58" s="58"/>
+      <c r="AE58" s="58"/>
+      <c r="AF58" s="59"/>
+      <c r="AG58" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH58" s="72"/>
+      <c r="AI58" s="72"/>
+      <c r="AJ58" s="72"/>
+      <c r="AK58" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL58" s="73"/>
+      <c r="AM58" s="73"/>
+      <c r="AN58" s="73"/>
+    </row>
+    <row r="59" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A59" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="68"/>
+      <c r="C59" s="68"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="70">
+        <v>6000</v>
+      </c>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70">
+        <v>1700</v>
+      </c>
+      <c r="I59" s="70"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="71">
+        <f t="shared" si="6"/>
+        <v>4300</v>
+      </c>
+      <c r="M59" s="72"/>
+      <c r="N59" s="72"/>
+      <c r="O59" s="72"/>
+      <c r="P59" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q59" s="73"/>
+      <c r="R59" s="73"/>
+      <c r="S59" s="73"/>
+      <c r="U59" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="V59" s="68"/>
+      <c r="W59" s="68"/>
+      <c r="X59" s="69"/>
+      <c r="Y59" s="47">
+        <v>6000</v>
+      </c>
+      <c r="Z59" s="70">
+        <v>6000</v>
+      </c>
+      <c r="AA59" s="70"/>
+      <c r="AB59" s="70"/>
+      <c r="AC59" s="70">
+        <v>6200</v>
+      </c>
+      <c r="AD59" s="70"/>
+      <c r="AE59" s="70"/>
+      <c r="AF59" s="70"/>
+      <c r="AG59" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH59" s="72"/>
+      <c r="AI59" s="72"/>
+      <c r="AJ59" s="72"/>
+      <c r="AK59" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL59" s="73"/>
+      <c r="AM59" s="73"/>
+      <c r="AN59" s="73"/>
+    </row>
+    <row r="60" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" s="68"/>
+      <c r="C60" s="68"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="70">
+        <v>7000</v>
+      </c>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70">
+        <v>1800</v>
+      </c>
+      <c r="I60" s="70"/>
+      <c r="J60" s="70"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="71">
+        <f t="shared" si="6"/>
+        <v>5200</v>
+      </c>
+      <c r="M60" s="72"/>
+      <c r="N60" s="72"/>
+      <c r="O60" s="72"/>
+      <c r="P60" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q60" s="73"/>
+      <c r="R60" s="73"/>
+      <c r="S60" s="73"/>
+      <c r="U60" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="V60" s="68"/>
+      <c r="W60" s="68"/>
+      <c r="X60" s="69"/>
+      <c r="Y60" s="47">
+        <v>7000</v>
+      </c>
+      <c r="Z60" s="70">
+        <v>7000</v>
+      </c>
+      <c r="AA60" s="70"/>
+      <c r="AB60" s="70"/>
+      <c r="AC60" s="70">
+        <v>8000</v>
+      </c>
+      <c r="AD60" s="70"/>
+      <c r="AE60" s="70"/>
+      <c r="AF60" s="70"/>
+      <c r="AG60" s="71">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="AH60" s="72"/>
+      <c r="AI60" s="72"/>
+      <c r="AJ60" s="72"/>
+      <c r="AK60" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL60" s="73"/>
+      <c r="AM60" s="73"/>
+      <c r="AN60" s="73"/>
+    </row>
+    <row r="61" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="70">
+        <v>8000</v>
+      </c>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70">
+        <v>1900</v>
+      </c>
+      <c r="I61" s="70"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="71">
+        <f t="shared" si="6"/>
+        <v>6100</v>
+      </c>
+      <c r="M61" s="72"/>
+      <c r="N61" s="72"/>
+      <c r="O61" s="72"/>
+      <c r="P61" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q61" s="73"/>
+      <c r="R61" s="73"/>
+      <c r="S61" s="73"/>
+      <c r="U61" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="V61" s="68"/>
+      <c r="W61" s="68"/>
+      <c r="X61" s="69"/>
+      <c r="Y61" s="47">
+        <v>8000</v>
+      </c>
+      <c r="Z61" s="70">
+        <v>8000</v>
+      </c>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="70"/>
+      <c r="AC61" s="57">
+        <v>8200</v>
+      </c>
+      <c r="AD61" s="58"/>
+      <c r="AE61" s="58"/>
+      <c r="AF61" s="59"/>
+      <c r="AG61" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH61" s="72"/>
+      <c r="AI61" s="72"/>
+      <c r="AJ61" s="72"/>
+      <c r="AK61" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL61" s="73"/>
+      <c r="AM61" s="73"/>
+      <c r="AN61" s="73"/>
+    </row>
+    <row r="62" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="70">
+        <v>9000</v>
+      </c>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70">
         <v>2000</v>
       </c>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54">
-        <v>1300</v>
-      </c>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="62">
-        <f t="shared" ref="L55:L71" si="4">E55-H55</f>
-        <v>700</v>
-      </c>
-      <c r="M55" s="63"/>
-      <c r="N55" s="63"/>
-      <c r="O55" s="63"/>
-      <c r="P55" s="61" t="s">
+      <c r="I62" s="70"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="71">
+        <f t="shared" si="6"/>
+        <v>7000</v>
+      </c>
+      <c r="M62" s="72"/>
+      <c r="N62" s="72"/>
+      <c r="O62" s="72"/>
+      <c r="P62" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q62" s="73"/>
+      <c r="R62" s="73"/>
+      <c r="S62" s="73"/>
+      <c r="U62" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="V62" s="68"/>
+      <c r="W62" s="68"/>
+      <c r="X62" s="69"/>
+      <c r="Y62" s="47">
+        <v>9000</v>
+      </c>
+      <c r="Z62" s="70">
+        <v>9000</v>
+      </c>
+      <c r="AA62" s="70"/>
+      <c r="AB62" s="70"/>
+      <c r="AC62" s="70">
+        <v>10000</v>
+      </c>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="70"/>
+      <c r="AF62" s="70"/>
+      <c r="AG62" s="71">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="AH62" s="72"/>
+      <c r="AI62" s="72"/>
+      <c r="AJ62" s="72"/>
+      <c r="AK62" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL62" s="73"/>
+      <c r="AM62" s="73"/>
+      <c r="AN62" s="73"/>
+    </row>
+    <row r="63" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="70">
+        <v>10000</v>
+      </c>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70">
+        <v>22100</v>
+      </c>
+      <c r="I63" s="70"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="71">
+        <f t="shared" si="6"/>
+        <v>-12100</v>
+      </c>
+      <c r="M63" s="72"/>
+      <c r="N63" s="72"/>
+      <c r="O63" s="72"/>
+      <c r="P63" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q63" s="79"/>
+      <c r="R63" s="79"/>
+      <c r="S63" s="79"/>
+      <c r="U63" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="V63" s="68"/>
+      <c r="W63" s="68"/>
+      <c r="X63" s="69"/>
+      <c r="Y63" s="47">
+        <v>10000</v>
+      </c>
+      <c r="Z63" s="70">
+        <v>10000</v>
+      </c>
+      <c r="AA63" s="70"/>
+      <c r="AB63" s="70"/>
+      <c r="AC63" s="70">
+        <v>10200</v>
+      </c>
+      <c r="AD63" s="70"/>
+      <c r="AE63" s="70"/>
+      <c r="AF63" s="70"/>
+      <c r="AG63" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH63" s="72"/>
+      <c r="AI63" s="72"/>
+      <c r="AJ63" s="72"/>
+      <c r="AK63" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL63" s="73"/>
+      <c r="AM63" s="73"/>
+      <c r="AN63" s="73"/>
+    </row>
+    <row r="64" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="70">
+        <v>11000</v>
+      </c>
+      <c r="F64" s="70"/>
+      <c r="G64" s="70"/>
+      <c r="H64" s="70">
+        <v>2200</v>
+      </c>
+      <c r="I64" s="70"/>
+      <c r="J64" s="70"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="71">
+        <f t="shared" si="6"/>
+        <v>8800</v>
+      </c>
+      <c r="M64" s="72"/>
+      <c r="N64" s="72"/>
+      <c r="O64" s="72"/>
+      <c r="P64" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q64" s="73"/>
+      <c r="R64" s="73"/>
+      <c r="S64" s="73"/>
+      <c r="U64" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="V64" s="68"/>
+      <c r="W64" s="68"/>
+      <c r="X64" s="69"/>
+      <c r="Y64" s="47">
+        <v>11000</v>
+      </c>
+      <c r="Z64" s="70">
+        <v>11000</v>
+      </c>
+      <c r="AA64" s="70"/>
+      <c r="AB64" s="70"/>
+      <c r="AC64" s="57">
+        <v>11200</v>
+      </c>
+      <c r="AD64" s="58"/>
+      <c r="AE64" s="58"/>
+      <c r="AF64" s="59"/>
+      <c r="AG64" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH64" s="72"/>
+      <c r="AI64" s="72"/>
+      <c r="AJ64" s="72"/>
+      <c r="AK64" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL64" s="73"/>
+      <c r="AM64" s="73"/>
+      <c r="AN64" s="73"/>
+    </row>
+    <row r="65" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="68"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="70">
+        <v>12000</v>
+      </c>
+      <c r="F65" s="70"/>
+      <c r="G65" s="70"/>
+      <c r="H65" s="70">
+        <v>22300</v>
+      </c>
+      <c r="I65" s="70"/>
+      <c r="J65" s="70"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="71">
+        <f t="shared" si="6"/>
+        <v>-10300</v>
+      </c>
+      <c r="M65" s="72"/>
+      <c r="N65" s="72"/>
+      <c r="O65" s="72"/>
+      <c r="P65" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q65" s="79"/>
+      <c r="R65" s="79"/>
+      <c r="S65" s="79"/>
+      <c r="U65" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="V65" s="68"/>
+      <c r="W65" s="68"/>
+      <c r="X65" s="69"/>
+      <c r="Y65" s="47">
+        <v>12000</v>
+      </c>
+      <c r="Z65" s="70">
+        <v>12000</v>
+      </c>
+      <c r="AA65" s="70"/>
+      <c r="AB65" s="70"/>
+      <c r="AC65" s="70">
+        <v>20000</v>
+      </c>
+      <c r="AD65" s="70"/>
+      <c r="AE65" s="70"/>
+      <c r="AF65" s="70"/>
+      <c r="AG65" s="71">
+        <f t="shared" si="7"/>
+        <v>8000</v>
+      </c>
+      <c r="AH65" s="72"/>
+      <c r="AI65" s="72"/>
+      <c r="AJ65" s="72"/>
+      <c r="AK65" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL65" s="73"/>
+      <c r="AM65" s="73"/>
+      <c r="AN65" s="73"/>
+    </row>
+    <row r="66" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="70">
+        <v>13000</v>
+      </c>
+      <c r="F66" s="70"/>
+      <c r="G66" s="70"/>
+      <c r="H66" s="70">
+        <v>22400</v>
+      </c>
+      <c r="I66" s="70"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="71">
+        <f t="shared" si="6"/>
+        <v>-9400</v>
+      </c>
+      <c r="M66" s="72"/>
+      <c r="N66" s="72"/>
+      <c r="O66" s="72"/>
+      <c r="P66" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q66" s="79"/>
+      <c r="R66" s="79"/>
+      <c r="S66" s="79"/>
+      <c r="U66" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="V66" s="68"/>
+      <c r="W66" s="68"/>
+      <c r="X66" s="69"/>
+      <c r="Y66" s="47">
+        <v>13000</v>
+      </c>
+      <c r="Z66" s="70">
+        <v>13000</v>
+      </c>
+      <c r="AA66" s="70"/>
+      <c r="AB66" s="70"/>
+      <c r="AC66" s="70">
+        <v>13200</v>
+      </c>
+      <c r="AD66" s="70"/>
+      <c r="AE66" s="70"/>
+      <c r="AF66" s="70"/>
+      <c r="AG66" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH66" s="72"/>
+      <c r="AI66" s="72"/>
+      <c r="AJ66" s="72"/>
+      <c r="AK66" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL66" s="73"/>
+      <c r="AM66" s="73"/>
+      <c r="AN66" s="73"/>
+    </row>
+    <row r="67" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="68"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="70">
+        <v>14000</v>
+      </c>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70">
+        <v>2500</v>
+      </c>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="71">
+        <f t="shared" si="6"/>
+        <v>11500</v>
+      </c>
+      <c r="M67" s="72"/>
+      <c r="N67" s="72"/>
+      <c r="O67" s="72"/>
+      <c r="P67" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="73"/>
+      <c r="U67" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="V67" s="68"/>
+      <c r="W67" s="68"/>
+      <c r="X67" s="69"/>
+      <c r="Y67" s="47">
+        <v>14000</v>
+      </c>
+      <c r="Z67" s="70">
+        <v>14000</v>
+      </c>
+      <c r="AA67" s="70"/>
+      <c r="AB67" s="70"/>
+      <c r="AC67" s="57">
+        <v>23000</v>
+      </c>
+      <c r="AD67" s="58"/>
+      <c r="AE67" s="58"/>
+      <c r="AF67" s="59"/>
+      <c r="AG67" s="71">
+        <f t="shared" si="7"/>
+        <v>9000</v>
+      </c>
+      <c r="AH67" s="72"/>
+      <c r="AI67" s="72"/>
+      <c r="AJ67" s="72"/>
+      <c r="AK67" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL67" s="73"/>
+      <c r="AM67" s="73"/>
+      <c r="AN67" s="73"/>
+    </row>
+    <row r="68" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="68"/>
+      <c r="C68" s="68"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="70">
+        <v>15000</v>
+      </c>
+      <c r="F68" s="70"/>
+      <c r="G68" s="70"/>
+      <c r="H68" s="70">
+        <v>2600</v>
+      </c>
+      <c r="I68" s="70"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="71">
+        <f t="shared" si="6"/>
+        <v>12400</v>
+      </c>
+      <c r="M68" s="72"/>
+      <c r="N68" s="72"/>
+      <c r="O68" s="72"/>
+      <c r="P68" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q68" s="73"/>
+      <c r="R68" s="73"/>
+      <c r="S68" s="73"/>
+      <c r="U68" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="V68" s="68"/>
+      <c r="W68" s="68"/>
+      <c r="X68" s="69"/>
+      <c r="Y68" s="47">
+        <v>15000</v>
+      </c>
+      <c r="Z68" s="70">
+        <v>15000</v>
+      </c>
+      <c r="AA68" s="70"/>
+      <c r="AB68" s="70"/>
+      <c r="AC68" s="70">
+        <v>15200</v>
+      </c>
+      <c r="AD68" s="70"/>
+      <c r="AE68" s="70"/>
+      <c r="AF68" s="70"/>
+      <c r="AG68" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH68" s="72"/>
+      <c r="AI68" s="72"/>
+      <c r="AJ68" s="72"/>
+      <c r="AK68" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL68" s="73"/>
+      <c r="AM68" s="73"/>
+      <c r="AN68" s="73"/>
+    </row>
+    <row r="69" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="70">
+        <v>16000</v>
+      </c>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="70">
+        <v>22700</v>
+      </c>
+      <c r="I69" s="70"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="71">
+        <f t="shared" si="6"/>
+        <v>-6700</v>
+      </c>
+      <c r="M69" s="72"/>
+      <c r="N69" s="72"/>
+      <c r="O69" s="72"/>
+      <c r="P69" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q69" s="79"/>
+      <c r="R69" s="79"/>
+      <c r="S69" s="79"/>
+      <c r="U69" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="V69" s="68"/>
+      <c r="W69" s="68"/>
+      <c r="X69" s="69"/>
+      <c r="Y69" s="47">
+        <v>16000</v>
+      </c>
+      <c r="Z69" s="70">
+        <v>16000</v>
+      </c>
+      <c r="AA69" s="70"/>
+      <c r="AB69" s="70"/>
+      <c r="AC69" s="70">
+        <v>16200</v>
+      </c>
+      <c r="AD69" s="70"/>
+      <c r="AE69" s="70"/>
+      <c r="AF69" s="70"/>
+      <c r="AG69" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH69" s="72"/>
+      <c r="AI69" s="72"/>
+      <c r="AJ69" s="72"/>
+      <c r="AK69" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL69" s="73"/>
+      <c r="AM69" s="73"/>
+      <c r="AN69" s="73"/>
+    </row>
+    <row r="70" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="70">
+        <v>17000</v>
+      </c>
+      <c r="F70" s="70"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="70">
+        <v>2800</v>
+      </c>
+      <c r="I70" s="70"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="71">
+        <f t="shared" si="6"/>
+        <v>14200</v>
+      </c>
+      <c r="M70" s="72"/>
+      <c r="N70" s="72"/>
+      <c r="O70" s="72"/>
+      <c r="P70" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q70" s="73"/>
+      <c r="R70" s="73"/>
+      <c r="S70" s="73"/>
+      <c r="U70" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="V70" s="68"/>
+      <c r="W70" s="68"/>
+      <c r="X70" s="69"/>
+      <c r="Y70" s="47">
+        <v>17000</v>
+      </c>
+      <c r="Z70" s="70">
+        <v>17000</v>
+      </c>
+      <c r="AA70" s="70"/>
+      <c r="AB70" s="70"/>
+      <c r="AC70" s="57">
+        <v>17200</v>
+      </c>
+      <c r="AD70" s="58"/>
+      <c r="AE70" s="58"/>
+      <c r="AF70" s="59"/>
+      <c r="AG70" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH70" s="72"/>
+      <c r="AI70" s="72"/>
+      <c r="AJ70" s="72"/>
+      <c r="AK70" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL70" s="73"/>
+      <c r="AM70" s="73"/>
+      <c r="AN70" s="73"/>
+    </row>
+    <row r="71" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="70">
+        <v>18000</v>
+      </c>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70">
+        <v>2900</v>
+      </c>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="71">
+        <f t="shared" si="6"/>
+        <v>15100</v>
+      </c>
+      <c r="M71" s="72"/>
+      <c r="N71" s="72"/>
+      <c r="O71" s="72"/>
+      <c r="P71" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q71" s="73"/>
+      <c r="R71" s="73"/>
+      <c r="S71" s="73"/>
+      <c r="U71" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="V71" s="68"/>
+      <c r="W71" s="68"/>
+      <c r="X71" s="69"/>
+      <c r="Y71" s="47">
+        <v>18000</v>
+      </c>
+      <c r="Z71" s="70">
+        <v>18000</v>
+      </c>
+      <c r="AA71" s="70"/>
+      <c r="AB71" s="70"/>
+      <c r="AC71" s="70">
+        <v>18200</v>
+      </c>
+      <c r="AD71" s="70"/>
+      <c r="AE71" s="70"/>
+      <c r="AF71" s="70"/>
+      <c r="AG71" s="71">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="AH71" s="72"/>
+      <c r="AI71" s="72"/>
+      <c r="AJ71" s="72"/>
+      <c r="AK71" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL71" s="73"/>
+      <c r="AM71" s="73"/>
+      <c r="AN71" s="73"/>
+    </row>
+    <row r="72" spans="1:40" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="74"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="75">
+        <f>AVERAGE(E54:G71)</f>
+        <v>9500</v>
+      </c>
+      <c r="F72" s="76"/>
+      <c r="G72" s="76"/>
+      <c r="H72" s="75">
+        <f>AVERAGE(H54:K71)</f>
+        <v>6494.4444444444443</v>
+      </c>
+      <c r="I72" s="76"/>
+      <c r="J72" s="76"/>
+      <c r="K72" s="76"/>
+      <c r="L72" s="75">
+        <f>AVERAGE(L54:O71)</f>
+        <v>3005.5555555555557</v>
+      </c>
+      <c r="M72" s="76"/>
+      <c r="N72" s="76"/>
+      <c r="O72" s="76"/>
+      <c r="U72" s="74"/>
+      <c r="V72" s="74"/>
+      <c r="W72" s="74"/>
+      <c r="X72" s="74"/>
+      <c r="Y72" s="46"/>
+      <c r="Z72" s="75">
+        <f>AVERAGE(Z54:AB71)</f>
+        <v>9500</v>
+      </c>
+      <c r="AA72" s="76"/>
+      <c r="AB72" s="76"/>
+      <c r="AC72" s="75">
+        <f>AVERAGE(AC54:AF71)</f>
+        <v>10700</v>
+      </c>
+      <c r="AD72" s="76"/>
+      <c r="AE72" s="76"/>
+      <c r="AF72" s="76"/>
+      <c r="AG72" s="75">
+        <f>AVERAGE(AG54:AJ71)</f>
+        <v>1200</v>
+      </c>
+      <c r="AH72" s="76"/>
+      <c r="AI72" s="76"/>
+      <c r="AJ72" s="76"/>
+    </row>
+    <row r="73" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="Q55" s="61"/>
-      <c r="R55" s="61"/>
-      <c r="S55" s="61"/>
-    </row>
-    <row r="56" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A56" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="59"/>
-      <c r="E56" s="54">
-        <v>3000</v>
-      </c>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54">
-        <v>1400</v>
-      </c>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="62">
-        <f t="shared" si="4"/>
-        <v>1600</v>
-      </c>
-      <c r="M56" s="63"/>
-      <c r="N56" s="63"/>
-      <c r="O56" s="63"/>
-      <c r="P56" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q56" s="61"/>
-      <c r="R56" s="61"/>
-      <c r="S56" s="61"/>
-    </row>
-    <row r="57" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A57" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="54">
-        <v>4000</v>
-      </c>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
-      <c r="H57" s="54">
-        <v>1500</v>
-      </c>
-      <c r="I57" s="54"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="54"/>
-      <c r="L57" s="62">
-        <f t="shared" si="4"/>
-        <v>2500</v>
-      </c>
-      <c r="M57" s="63"/>
-      <c r="N57" s="63"/>
-      <c r="O57" s="63"/>
-      <c r="P57" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q57" s="61"/>
-      <c r="R57" s="61"/>
-      <c r="S57" s="61"/>
-    </row>
-    <row r="58" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="54">
-        <v>5000</v>
-      </c>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54">
-        <v>1600</v>
-      </c>
-      <c r="I58" s="54"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="54"/>
-      <c r="L58" s="62">
-        <f t="shared" si="4"/>
-        <v>3400</v>
-      </c>
-      <c r="M58" s="63"/>
-      <c r="N58" s="63"/>
-      <c r="O58" s="63"/>
-      <c r="P58" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q58" s="61"/>
-      <c r="R58" s="61"/>
-      <c r="S58" s="61"/>
-    </row>
-    <row r="59" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="59"/>
-      <c r="E59" s="54">
-        <v>6000</v>
-      </c>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54">
-        <v>1700</v>
-      </c>
-      <c r="I59" s="54"/>
-      <c r="J59" s="54"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="62">
-        <f t="shared" si="4"/>
-        <v>4300</v>
-      </c>
-      <c r="M59" s="63"/>
-      <c r="N59" s="63"/>
-      <c r="O59" s="63"/>
-      <c r="P59" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q59" s="61"/>
-      <c r="R59" s="61"/>
-      <c r="S59" s="61"/>
-    </row>
-    <row r="60" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A60" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="54">
-        <v>7000</v>
-      </c>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54">
-        <v>1800</v>
-      </c>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="62">
-        <f t="shared" si="4"/>
-        <v>5200</v>
-      </c>
-      <c r="M60" s="63"/>
-      <c r="N60" s="63"/>
-      <c r="O60" s="63"/>
-      <c r="P60" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q60" s="61"/>
-      <c r="R60" s="61"/>
-      <c r="S60" s="61"/>
-    </row>
-    <row r="61" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="54">
-        <v>8000</v>
-      </c>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="54">
-        <v>1900</v>
-      </c>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
-      <c r="L61" s="62">
-        <f t="shared" si="4"/>
-        <v>6100</v>
-      </c>
-      <c r="M61" s="63"/>
-      <c r="N61" s="63"/>
-      <c r="O61" s="63"/>
-      <c r="P61" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q61" s="61"/>
-      <c r="R61" s="61"/>
-      <c r="S61" s="61"/>
-    </row>
-    <row r="62" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A62" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="54">
-        <v>9000</v>
-      </c>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
-      <c r="H62" s="54">
-        <v>2000</v>
-      </c>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="L62" s="62">
-        <f t="shared" si="4"/>
-        <v>7000</v>
-      </c>
-      <c r="M62" s="63"/>
-      <c r="N62" s="63"/>
-      <c r="O62" s="63"/>
-      <c r="P62" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q62" s="61"/>
-      <c r="R62" s="61"/>
-      <c r="S62" s="61"/>
-    </row>
-    <row r="63" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A63" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="59"/>
-      <c r="E63" s="54">
-        <v>10000</v>
-      </c>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
-      <c r="H63" s="54">
-        <v>22100</v>
-      </c>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="L63" s="62">
-        <f t="shared" si="4"/>
-        <v>-12100</v>
-      </c>
-      <c r="M63" s="63"/>
-      <c r="N63" s="63"/>
-      <c r="O63" s="63"/>
-      <c r="P63" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q63" s="60"/>
-      <c r="R63" s="60"/>
-      <c r="S63" s="60"/>
-    </row>
-    <row r="64" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A64" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="54">
-        <v>11000</v>
-      </c>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54">
-        <v>2200</v>
-      </c>
-      <c r="I64" s="54"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
-      <c r="L64" s="62">
-        <f t="shared" si="4"/>
-        <v>8800</v>
-      </c>
-      <c r="M64" s="63"/>
-      <c r="N64" s="63"/>
-      <c r="O64" s="63"/>
-      <c r="P64" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q64" s="61"/>
-      <c r="R64" s="61"/>
-      <c r="S64" s="61"/>
-    </row>
-    <row r="65" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="59"/>
-      <c r="E65" s="54">
-        <v>12000</v>
-      </c>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="54">
-        <v>22300</v>
-      </c>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-      <c r="K65" s="54"/>
-      <c r="L65" s="62">
-        <f t="shared" si="4"/>
-        <v>-10300</v>
-      </c>
-      <c r="M65" s="63"/>
-      <c r="N65" s="63"/>
-      <c r="O65" s="63"/>
-      <c r="P65" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q65" s="60"/>
-      <c r="R65" s="60"/>
-      <c r="S65" s="60"/>
-    </row>
-    <row r="66" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A66" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="54">
-        <v>13000</v>
-      </c>
-      <c r="F66" s="54"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="54">
-        <v>22400</v>
-      </c>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="54"/>
-      <c r="L66" s="62">
-        <f t="shared" si="4"/>
-        <v>-9400</v>
-      </c>
-      <c r="M66" s="63"/>
-      <c r="N66" s="63"/>
-      <c r="O66" s="63"/>
-      <c r="P66" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q66" s="60"/>
-      <c r="R66" s="60"/>
-      <c r="S66" s="60"/>
-    </row>
-    <row r="67" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="54">
-        <v>14000</v>
-      </c>
-      <c r="F67" s="54"/>
-      <c r="G67" s="54"/>
-      <c r="H67" s="54">
-        <v>2500</v>
-      </c>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-      <c r="K67" s="54"/>
-      <c r="L67" s="62">
-        <f t="shared" si="4"/>
-        <v>11500</v>
-      </c>
-      <c r="M67" s="63"/>
-      <c r="N67" s="63"/>
-      <c r="O67" s="63"/>
-      <c r="P67" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q67" s="61"/>
-      <c r="R67" s="61"/>
-      <c r="S67" s="61"/>
-    </row>
-    <row r="68" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="54">
-        <v>15000</v>
-      </c>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54">
-        <v>2600</v>
-      </c>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
-      <c r="L68" s="62">
-        <f t="shared" si="4"/>
-        <v>12400</v>
-      </c>
-      <c r="M68" s="63"/>
-      <c r="N68" s="63"/>
-      <c r="O68" s="63"/>
-      <c r="P68" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q68" s="61"/>
-      <c r="R68" s="61"/>
-      <c r="S68" s="61"/>
-    </row>
-    <row r="69" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="54">
-        <v>16000</v>
-      </c>
-      <c r="F69" s="54"/>
-      <c r="G69" s="54"/>
-      <c r="H69" s="54">
-        <v>22700</v>
-      </c>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
-      <c r="L69" s="62">
-        <f t="shared" si="4"/>
-        <v>-6700</v>
-      </c>
-      <c r="M69" s="63"/>
-      <c r="N69" s="63"/>
-      <c r="O69" s="63"/>
-      <c r="P69" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q69" s="60"/>
-      <c r="R69" s="60"/>
-      <c r="S69" s="60"/>
-    </row>
-    <row r="70" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="54">
-        <v>17000</v>
-      </c>
-      <c r="F70" s="54"/>
-      <c r="G70" s="54"/>
-      <c r="H70" s="54">
-        <v>2800</v>
-      </c>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
-      <c r="L70" s="62">
-        <f t="shared" si="4"/>
-        <v>14200</v>
-      </c>
-      <c r="M70" s="63"/>
-      <c r="N70" s="63"/>
-      <c r="O70" s="63"/>
-      <c r="P70" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q70" s="61"/>
-      <c r="R70" s="61"/>
-      <c r="S70" s="61"/>
-    </row>
-    <row r="71" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="54">
-        <v>18000</v>
-      </c>
-      <c r="F71" s="54"/>
-      <c r="G71" s="54"/>
-      <c r="H71" s="54">
-        <v>2900</v>
-      </c>
-      <c r="I71" s="54"/>
-      <c r="J71" s="54"/>
-      <c r="K71" s="54"/>
-      <c r="L71" s="62">
-        <f t="shared" si="4"/>
-        <v>15100</v>
-      </c>
-      <c r="M71" s="63"/>
-      <c r="N71" s="63"/>
-      <c r="O71" s="63"/>
-      <c r="P71" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q71" s="61"/>
-      <c r="R71" s="61"/>
-      <c r="S71" s="61"/>
-    </row>
-    <row r="72" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A72" s="52"/>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-      <c r="L72" s="53"/>
-      <c r="M72" s="53"/>
-      <c r="N72" s="53"/>
-      <c r="O72" s="53"/>
-    </row>
-    <row r="73" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="B73" s="66"/>
-      <c r="C73" s="66">
+      <c r="B73" s="62"/>
+      <c r="C73" s="62">
         <f>COUNTA(A54:D71)</f>
         <v>18</v>
       </c>
-      <c r="D73" s="66"/>
-      <c r="E73" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="F73" s="70">
+      <c r="D73" s="62"/>
+      <c r="E73" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="87">
         <f>SUM(E54:G71)</f>
         <v>171000</v>
       </c>
-      <c r="G73" s="67"/>
-      <c r="H73" s="68" t="s">
-        <v>101</v>
-      </c>
-      <c r="I73" s="68"/>
-      <c r="J73" s="69">
+      <c r="G73" s="63"/>
+      <c r="H73" s="65" t="s">
+        <v>100</v>
+      </c>
+      <c r="I73" s="65"/>
+      <c r="J73" s="66">
         <f>SUM(H54:K71)</f>
         <v>116900</v>
       </c>
-      <c r="K73" s="68"/>
-      <c r="L73" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="M73" s="55"/>
-      <c r="N73" s="71">
+      <c r="K73" s="65"/>
+      <c r="L73" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="M73" s="50"/>
+      <c r="N73" s="49">
         <f>F73-J73</f>
         <v>54100</v>
       </c>
-      <c r="O73" s="55"/>
-      <c r="P73" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q73" s="55"/>
-      <c r="R73" s="71" t="str">
+      <c r="O73" s="50"/>
+      <c r="P73" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q73" s="50"/>
+      <c r="R73" s="49" t="str">
         <f>IF(N73&gt;=50000,"Good","Bad")</f>
         <v>Good</v>
       </c>
-      <c r="S73" s="55"/>
+      <c r="S73" s="50"/>
+      <c r="U73" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="V73" s="62"/>
+      <c r="W73" s="62">
+        <f>COUNTA(U54:X71)</f>
+        <v>18</v>
+      </c>
+      <c r="X73" s="62"/>
+      <c r="Y73" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z73" s="64">
+        <f>SUM(Y54:Y71)</f>
+        <v>171000</v>
+      </c>
+      <c r="AA73" s="64"/>
+      <c r="AB73" s="65" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC73" s="65"/>
+      <c r="AD73" s="66">
+        <f>SUM(Z54:AB71)</f>
+        <v>171000</v>
+      </c>
+      <c r="AE73" s="65"/>
+      <c r="AF73" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG73" s="50"/>
+      <c r="AH73" s="49">
+        <f>SUM(AG54:AJ71)</f>
+        <v>21600</v>
+      </c>
+      <c r="AI73" s="50"/>
+      <c r="AJ73" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK73" s="50"/>
+      <c r="AL73" s="49" t="str">
+        <f>IF(AH73&gt;0,"Profit","Loss")</f>
+        <v>Profit</v>
+      </c>
+      <c r="AM73" s="50"/>
     </row>
-    <row r="74" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="66"/>
-      <c r="B74" s="66"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="67"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="68"/>
-      <c r="I74" s="68"/>
-      <c r="J74" s="68"/>
-      <c r="K74" s="68"/>
-      <c r="L74" s="55"/>
-      <c r="M74" s="55"/>
-      <c r="N74" s="55"/>
-      <c r="O74" s="55"/>
-      <c r="P74" s="55"/>
-      <c r="Q74" s="55"/>
-      <c r="R74" s="55"/>
-      <c r="S74" s="55"/>
+    <row r="74" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="62"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="62"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="65"/>
+      <c r="L74" s="50"/>
+      <c r="M74" s="50"/>
+      <c r="N74" s="50"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="50"/>
+      <c r="Q74" s="50"/>
+      <c r="R74" s="50"/>
+      <c r="S74" s="50"/>
+      <c r="U74" s="62"/>
+      <c r="V74" s="62"/>
+      <c r="W74" s="62"/>
+      <c r="X74" s="62"/>
+      <c r="Y74" s="63"/>
+      <c r="Z74" s="64"/>
+      <c r="AA74" s="64"/>
+      <c r="AB74" s="65"/>
+      <c r="AC74" s="65"/>
+      <c r="AD74" s="65"/>
+      <c r="AE74" s="65"/>
+      <c r="AF74" s="50"/>
+      <c r="AG74" s="50"/>
+      <c r="AH74" s="50"/>
+      <c r="AI74" s="50"/>
+      <c r="AJ74" s="50"/>
+      <c r="AK74" s="50"/>
+      <c r="AL74" s="50"/>
+      <c r="AM74" s="50"/>
     </row>
-    <row r="75" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
-      <c r="O75" s="10"/>
+      <c r="E75" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="52">
+        <f>_xlfn.PERCENTOF(J73,F73)</f>
+        <v>0.68362573099415203</v>
+      </c>
+      <c r="I75" s="52"/>
+      <c r="J75" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="K75" s="53"/>
+      <c r="L75" s="53"/>
+      <c r="M75" s="54">
+        <f>1-H75</f>
+        <v>0.31637426900584797</v>
+      </c>
+      <c r="N75" s="54"/>
+      <c r="O75" s="48"/>
+      <c r="U75" s="10"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="X75" s="60"/>
+      <c r="Y75" s="61">
+        <f>MAX(AG54:AJ71)</f>
+        <v>9000</v>
+      </c>
+      <c r="Z75" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA75" s="51"/>
+      <c r="AB75" s="51"/>
+      <c r="AC75" s="52">
+        <f>_xlfn.PERCENTOF(AH73,AD73)</f>
+        <v>0.12631578947368421</v>
+      </c>
+      <c r="AD75" s="52"/>
+      <c r="AE75" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF75" s="53"/>
+      <c r="AG75" s="53"/>
+      <c r="AH75" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI75" s="54"/>
+      <c r="AJ75" s="48"/>
     </row>
-    <row r="79" spans="1:19" ht="32" x14ac:dyDescent="0.4">
-      <c r="I79" s="51"/>
+    <row r="76" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="53"/>
+      <c r="M76" s="54"/>
+      <c r="N76" s="54"/>
+      <c r="W76" s="60"/>
+      <c r="X76" s="60"/>
+      <c r="Y76" s="60"/>
+      <c r="Z76" s="51"/>
+      <c r="AA76" s="51"/>
+      <c r="AB76" s="51"/>
+      <c r="AC76" s="52"/>
+      <c r="AD76" s="52"/>
+      <c r="AE76" s="53"/>
+      <c r="AF76" s="53"/>
+      <c r="AG76" s="53"/>
+      <c r="AH76" s="54"/>
+      <c r="AI76" s="54"/>
+    </row>
+    <row r="79" spans="1:40" ht="32" x14ac:dyDescent="0.4">
+      <c r="I79" s="45"/>
     </row>
   </sheetData>
-  <autoFilter ref="A52:S71" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
+  <autoFilter ref="A52:AN72" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
     <filterColumn colId="0" showButton="0"/>
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="2" showButton="0"/>
@@ -9195,6 +15337,20 @@
     <filterColumn colId="15" showButton="0"/>
     <filterColumn colId="16" showButton="0"/>
     <filterColumn colId="17" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="21" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
+    <filterColumn colId="25" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+    <filterColumn colId="28" showButton="0"/>
+    <filterColumn colId="29" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="33" showButton="0"/>
+    <filterColumn colId="34" showButton="0"/>
+    <filterColumn colId="36" showButton="0"/>
+    <filterColumn colId="37" showButton="0"/>
+    <filterColumn colId="38" showButton="0"/>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:K15">
     <sortCondition ref="A4:A15"/>
@@ -9202,8 +15358,7 @@
     <sortCondition ref="C4:C15"/>
     <sortCondition ref="I4:I15"/>
   </sortState>
-  <mergeCells count="116">
-    <mergeCell ref="P73:Q74"/>
+  <mergeCells count="237">
     <mergeCell ref="A47:S49"/>
     <mergeCell ref="R73:S74"/>
     <mergeCell ref="L66:O66"/>
@@ -9227,6 +15382,14 @@
     <mergeCell ref="N73:O74"/>
     <mergeCell ref="E73:E74"/>
     <mergeCell ref="F73:G74"/>
+    <mergeCell ref="P65:S65"/>
+    <mergeCell ref="P66:S66"/>
+    <mergeCell ref="P67:S67"/>
+    <mergeCell ref="P58:S58"/>
+    <mergeCell ref="P59:S59"/>
+    <mergeCell ref="P60:S60"/>
+    <mergeCell ref="P61:S61"/>
+    <mergeCell ref="P62:S62"/>
     <mergeCell ref="H73:I74"/>
     <mergeCell ref="J73:K74"/>
     <mergeCell ref="L73:M74"/>
@@ -9236,16 +15399,7 @@
     <mergeCell ref="P71:S71"/>
     <mergeCell ref="L72:O72"/>
     <mergeCell ref="L71:O71"/>
-    <mergeCell ref="P63:S63"/>
-    <mergeCell ref="P64:S64"/>
-    <mergeCell ref="P65:S65"/>
-    <mergeCell ref="P66:S66"/>
-    <mergeCell ref="P67:S67"/>
-    <mergeCell ref="P58:S58"/>
-    <mergeCell ref="P59:S59"/>
-    <mergeCell ref="P60:S60"/>
-    <mergeCell ref="P61:S61"/>
-    <mergeCell ref="P62:S62"/>
+    <mergeCell ref="P73:Q74"/>
     <mergeCell ref="H67:K67"/>
     <mergeCell ref="H68:K68"/>
     <mergeCell ref="H69:K69"/>
@@ -9287,6 +15441,32 @@
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="P57:S57"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="P54:S54"/>
+    <mergeCell ref="P63:S63"/>
+    <mergeCell ref="P64:S64"/>
+    <mergeCell ref="P55:S55"/>
+    <mergeCell ref="P56:S56"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="H75:I76"/>
+    <mergeCell ref="E75:G76"/>
+    <mergeCell ref="J75:L76"/>
+    <mergeCell ref="M75:N76"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="H72:K72"/>
     <mergeCell ref="A73:B74"/>
@@ -9299,30 +15479,188 @@
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="P57:S57"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="P54:S54"/>
-    <mergeCell ref="P55:S55"/>
-    <mergeCell ref="P56:S56"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="U47:AN49"/>
+    <mergeCell ref="U52:X53"/>
+    <mergeCell ref="Z52:AB53"/>
+    <mergeCell ref="AC52:AF53"/>
+    <mergeCell ref="AG52:AJ53"/>
+    <mergeCell ref="AK52:AN53"/>
+    <mergeCell ref="U54:X54"/>
+    <mergeCell ref="Z54:AB54"/>
+    <mergeCell ref="AG54:AJ54"/>
+    <mergeCell ref="AK54:AN54"/>
+    <mergeCell ref="U55:X55"/>
+    <mergeCell ref="Z55:AB55"/>
+    <mergeCell ref="AC54:AF54"/>
+    <mergeCell ref="AG55:AJ55"/>
+    <mergeCell ref="AK55:AN55"/>
+    <mergeCell ref="U56:X56"/>
+    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="AC56:AF56"/>
+    <mergeCell ref="AG56:AJ56"/>
+    <mergeCell ref="AK56:AN56"/>
+    <mergeCell ref="U57:X57"/>
+    <mergeCell ref="Z57:AB57"/>
+    <mergeCell ref="AC57:AF57"/>
+    <mergeCell ref="AG57:AJ57"/>
+    <mergeCell ref="AK57:AN57"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="AC58:AF58"/>
+    <mergeCell ref="AG58:AJ58"/>
+    <mergeCell ref="AK58:AN58"/>
+    <mergeCell ref="U59:X59"/>
+    <mergeCell ref="Z59:AB59"/>
+    <mergeCell ref="AC59:AF59"/>
+    <mergeCell ref="AG59:AJ59"/>
+    <mergeCell ref="AK59:AN59"/>
+    <mergeCell ref="U60:X60"/>
+    <mergeCell ref="Z60:AB60"/>
+    <mergeCell ref="AC60:AF60"/>
+    <mergeCell ref="AG60:AJ60"/>
+    <mergeCell ref="AK60:AN60"/>
+    <mergeCell ref="U61:X61"/>
+    <mergeCell ref="Z61:AB61"/>
+    <mergeCell ref="AC61:AF61"/>
+    <mergeCell ref="AG61:AJ61"/>
+    <mergeCell ref="AK61:AN61"/>
+    <mergeCell ref="U62:X62"/>
+    <mergeCell ref="Z62:AB62"/>
+    <mergeCell ref="AC62:AF62"/>
+    <mergeCell ref="AG62:AJ62"/>
+    <mergeCell ref="AK62:AN62"/>
+    <mergeCell ref="U63:X63"/>
+    <mergeCell ref="Z63:AB63"/>
+    <mergeCell ref="AC63:AF63"/>
+    <mergeCell ref="AG63:AJ63"/>
+    <mergeCell ref="AK63:AN63"/>
+    <mergeCell ref="U64:X64"/>
+    <mergeCell ref="Z64:AB64"/>
+    <mergeCell ref="AC64:AF64"/>
+    <mergeCell ref="AG64:AJ64"/>
+    <mergeCell ref="AK64:AN64"/>
+    <mergeCell ref="U65:X65"/>
+    <mergeCell ref="Z65:AB65"/>
+    <mergeCell ref="AC65:AF65"/>
+    <mergeCell ref="AG65:AJ65"/>
+    <mergeCell ref="AK65:AN65"/>
+    <mergeCell ref="U66:X66"/>
+    <mergeCell ref="Z66:AB66"/>
+    <mergeCell ref="AC66:AF66"/>
+    <mergeCell ref="AG66:AJ66"/>
+    <mergeCell ref="AK66:AN66"/>
+    <mergeCell ref="Z70:AB70"/>
+    <mergeCell ref="AC70:AF70"/>
+    <mergeCell ref="AG70:AJ70"/>
+    <mergeCell ref="AK70:AN70"/>
+    <mergeCell ref="U67:X67"/>
+    <mergeCell ref="Z67:AB67"/>
+    <mergeCell ref="AC67:AF67"/>
+    <mergeCell ref="AG67:AJ67"/>
+    <mergeCell ref="AK67:AN67"/>
+    <mergeCell ref="U68:X68"/>
+    <mergeCell ref="Z68:AB68"/>
+    <mergeCell ref="AC68:AF68"/>
+    <mergeCell ref="AG68:AJ68"/>
+    <mergeCell ref="AK68:AN68"/>
+    <mergeCell ref="U73:V74"/>
+    <mergeCell ref="W73:X74"/>
+    <mergeCell ref="Y73:Y74"/>
+    <mergeCell ref="Z73:AA74"/>
+    <mergeCell ref="AB73:AC74"/>
+    <mergeCell ref="AD73:AE74"/>
+    <mergeCell ref="AF73:AG74"/>
+    <mergeCell ref="AH73:AI74"/>
+    <mergeCell ref="AJ73:AK74"/>
+    <mergeCell ref="AL73:AM74"/>
+    <mergeCell ref="Z75:AB76"/>
+    <mergeCell ref="AC75:AD76"/>
+    <mergeCell ref="AE75:AG76"/>
+    <mergeCell ref="AH75:AI76"/>
+    <mergeCell ref="Y52:Y53"/>
+    <mergeCell ref="AC55:AF55"/>
+    <mergeCell ref="W75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="U71:X71"/>
+    <mergeCell ref="Z71:AB71"/>
+    <mergeCell ref="AC71:AF71"/>
+    <mergeCell ref="AG71:AJ71"/>
+    <mergeCell ref="AK71:AN71"/>
+    <mergeCell ref="U72:X72"/>
+    <mergeCell ref="Z72:AB72"/>
+    <mergeCell ref="AC72:AF72"/>
+    <mergeCell ref="AG72:AJ72"/>
+    <mergeCell ref="U69:X69"/>
+    <mergeCell ref="Z69:AB69"/>
+    <mergeCell ref="AC69:AF69"/>
+    <mergeCell ref="AG69:AJ69"/>
+    <mergeCell ref="AK69:AN69"/>
+    <mergeCell ref="U70:X70"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="D3:D15">
+    <cfRule type="iconSet" priority="30">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E54:G71">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H54:K71">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="9"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3:I15">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9334,7 +15672,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9346,24 +15684,91 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K15">
-    <cfRule type="duplicateValues" dxfId="24" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="uniqueValues" dxfId="23" priority="20"/>
+    <cfRule type="uniqueValues" dxfId="14" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB3:AB14">
-    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
+  <conditionalFormatting sqref="L54:O71">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="22" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB8">
-    <cfRule type="uniqueValues" dxfId="21" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D15">
-    <cfRule type="iconSet" priority="13">
+  <conditionalFormatting sqref="P54:S71">
+    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",P54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="iconSet" priority="28">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
         <cfvo type="percent" val="67"/>
       </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z54:AB71">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC3:AC14">
+    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC8">
+    <cfRule type="uniqueValues" dxfId="7" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC54:AF54 AC71:AF71 AC56:AF57 AC59:AF60 AC62:AF63 AC65:AF66 AC68:AF69">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
@@ -9376,32 +15781,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P54:S71">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Bad">
-      <formula>NOT(ISERROR(SEARCH("Bad",P54)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="iconSet" priority="11">
-      <iconSet>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="AC54:AF71">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9412,26 +15793,48 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H54:K71">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color theme="9"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
+  <conditionalFormatting sqref="AG54:AJ71">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG54:AN54">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK54:AN71">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",AK54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",AK54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="iconSet" priority="16">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9440,26 +15843,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E54:G71">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L54:O71">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="greaterThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/eXCEL.xlsx
+++ b/eXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB274DC-8E8F-DF43-8E8B-52C179703550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5959DEE4-FAAE-7843-89BB-AF1819D73FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14020" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="25600" windowHeight="14000" activeTab="2" xr2:uid="{BFF67E27-97A4-2742-884B-996DB741DDCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -20,11 +20,45 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$52:$AN$72</definedName>
+    <definedName name="_xlchart.v5.0" hidden="1">Sheet1!$A$108:$A$118</definedName>
+    <definedName name="_xlchart.v5.1" hidden="1">Sheet1!$A$119</definedName>
+    <definedName name="_xlchart.v5.10" hidden="1">Sheet1!$B$120:$D$120</definedName>
+    <definedName name="_xlchart.v5.11" hidden="1">Sheet1!$B$121:$D$121</definedName>
+    <definedName name="_xlchart.v5.12" hidden="1">Sheet1!$B$122:$D$122</definedName>
+    <definedName name="_xlchart.v5.13" hidden="1">Sheet1!$B$123:$D$123</definedName>
+    <definedName name="_xlchart.v5.14" hidden="1">Sheet1!$B$124:$D$124</definedName>
+    <definedName name="_xlchart.v5.15" hidden="1">Sheet1!$B$125:$D$125</definedName>
+    <definedName name="_xlchart.v5.16" hidden="1">Sheet1!$A$108:$A$118</definedName>
+    <definedName name="_xlchart.v5.17" hidden="1">Sheet1!$A$119</definedName>
+    <definedName name="_xlchart.v5.18" hidden="1">Sheet1!$A$120</definedName>
+    <definedName name="_xlchart.v5.19" hidden="1">Sheet1!$A$121</definedName>
+    <definedName name="_xlchart.v5.2" hidden="1">Sheet1!$A$120</definedName>
+    <definedName name="_xlchart.v5.20" hidden="1">Sheet1!$A$122</definedName>
+    <definedName name="_xlchart.v5.21" hidden="1">Sheet1!$A$123</definedName>
+    <definedName name="_xlchart.v5.22" hidden="1">Sheet1!$A$124</definedName>
+    <definedName name="_xlchart.v5.23" hidden="1">Sheet1!$A$125</definedName>
+    <definedName name="_xlchart.v5.24" hidden="1">Sheet1!$B$108:$D$118</definedName>
+    <definedName name="_xlchart.v5.25" hidden="1">Sheet1!$B$119:$D$119</definedName>
+    <definedName name="_xlchart.v5.26" hidden="1">Sheet1!$B$120:$D$120</definedName>
+    <definedName name="_xlchart.v5.27" hidden="1">Sheet1!$B$121:$D$121</definedName>
+    <definedName name="_xlchart.v5.28" hidden="1">Sheet1!$B$122:$D$122</definedName>
+    <definedName name="_xlchart.v5.29" hidden="1">Sheet1!$B$123:$D$123</definedName>
+    <definedName name="_xlchart.v5.3" hidden="1">Sheet1!$A$121</definedName>
+    <definedName name="_xlchart.v5.30" hidden="1">Sheet1!$B$124:$D$124</definedName>
+    <definedName name="_xlchart.v5.31" hidden="1">Sheet1!$B$125:$D$125</definedName>
+    <definedName name="_xlchart.v5.32" hidden="1">Sheet1!$E$3</definedName>
+    <definedName name="_xlchart.v5.33" hidden="1">Sheet1!$E$4:$E$15</definedName>
+    <definedName name="_xlchart.v5.4" hidden="1">Sheet1!$A$122</definedName>
+    <definedName name="_xlchart.v5.5" hidden="1">Sheet1!$A$123</definedName>
+    <definedName name="_xlchart.v5.6" hidden="1">Sheet1!$A$124</definedName>
+    <definedName name="_xlchart.v5.7" hidden="1">Sheet1!$A$125</definedName>
+    <definedName name="_xlchart.v5.8" hidden="1">Sheet1!$B$108:$D$118</definedName>
+    <definedName name="_xlchart.v5.9" hidden="1">Sheet1!$B$119:$D$119</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId5"/>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -65,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="143">
   <si>
     <t>Sno</t>
   </si>
@@ -485,6 +519,15 @@
   </si>
   <si>
     <t>Max_Profit:</t>
+  </si>
+  <si>
+    <t>DASH_BOARD-3(Country)</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>America</t>
   </si>
 </sst>
 </file>
@@ -994,21 +1037,6 @@
     <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1031,6 +1059,21 @@
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1069,7 +1112,147 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1152,11 +1335,71 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1192,11 +1435,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1207,6 +1450,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11859,7 +12112,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63FA6F72-851F-AE4F-BD1A-ECCEC263B233}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" numFmtId="2" showAll="0">
@@ -11974,7 +12227,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE88B321-F2D6-4B43-A0B4-46F838A82FEF}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -12015,27 +12268,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}" name="Table1" displayName="Table1" ref="A2:L15" totalsRowShown="0" headerRowBorderDxfId="52" tableBorderDxfId="51" totalsRowBorderDxfId="50">
   <autoFilter ref="A2:L15" xr:uid="{4890AB8F-5E94-8141-9A15-A5C03CA2EEB0}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="doj" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{83FAB420-09E3-4946-A54F-7BEB37205C54}" name="Column1" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{9525A124-35F8-CE47-B091-51D4F1F7BE37}" name="Column2" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{30657457-B4E0-D84A-8FC4-728FE95F70A0}" name="Column3" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{8B82043D-8611-2C44-AFE7-009A93D6FED9}" name="Column4" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{70F5AED1-9DFC-EB49-ADA0-35FF2152CE0A}" name="doj" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{538AD498-8499-4543-B773-A1000636000E}" name="Column6" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{5240A1DB-DFDE-F640-9A4C-49D03B35AB86}" name="Column7" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{0166B8A7-22CA-6344-94FC-B2CC5926BB84}" name="Column8" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{329BE943-F433-8F48-90E3-1C53E049088B}" name="Column9" dataDxfId="41">
       <calculatedColumnFormula>SUM(F3+G3+H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="19">
+    <tableColumn id="10" xr3:uid="{C1CB1439-25DA-784F-BD26-296D7ACBF756}" name="Column10" dataDxfId="40">
       <calculatedColumnFormula>AVERAGE(F3:H3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="18">
+    <tableColumn id="11" xr3:uid="{EB12A6BE-3C5A-3440-AE13-4066A2489121}" name="Column11" dataDxfId="39">
       <calculatedColumnFormula>CONCATENATE(B3,"  ",C3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="17">
+    <tableColumn id="12" xr3:uid="{E4BDC5FC-D539-C341-9C86-C64B7529797A}" name="Column12" dataDxfId="38">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Column10]]&gt;1800,"Good","Bad")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12066,7 +12319,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}" name="Table5" displayName="Table5" ref="M4:P9" totalsRowShown="0" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}" name="Table5" displayName="Table5" ref="M4:P9" totalsRowShown="0" tableBorderDxfId="37">
   <autoFilter ref="M4:P9" xr:uid="{BE567F3B-4F17-E14B-99AB-98197F28EF0D}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2E8124BF-9EED-0049-9B4E-570F10E09411}" name="Column1"/>
@@ -12549,7 +12802,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="28.1640625" customWidth="1"/>
@@ -13886,63 +14139,63 @@
       <c r="AN53" s="78"/>
     </row>
     <row r="54" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="69"/>
-      <c r="E54" s="70">
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="65">
         <v>1000</v>
       </c>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
       <c r="H54" s="86">
         <v>1200</v>
       </c>
       <c r="I54" s="86"/>
       <c r="J54" s="86"/>
       <c r="K54" s="86"/>
-      <c r="L54" s="71">
+      <c r="L54" s="66">
         <f>E54-H54</f>
         <v>-200</v>
       </c>
-      <c r="M54" s="72"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="72"/>
+      <c r="M54" s="67"/>
+      <c r="N54" s="67"/>
+      <c r="O54" s="67"/>
       <c r="P54" s="79" t="s">
         <v>101</v>
       </c>
       <c r="Q54" s="79"/>
       <c r="R54" s="79"/>
       <c r="S54" s="79"/>
-      <c r="U54" s="67" t="s">
+      <c r="U54" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="V54" s="68"/>
-      <c r="W54" s="68"/>
-      <c r="X54" s="69"/>
+      <c r="V54" s="63"/>
+      <c r="W54" s="63"/>
+      <c r="X54" s="64"/>
       <c r="Y54" s="47">
         <v>1000</v>
       </c>
-      <c r="Z54" s="70">
+      <c r="Z54" s="65">
         <v>1000</v>
       </c>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="70"/>
-      <c r="AC54" s="70">
+      <c r="AA54" s="65"/>
+      <c r="AB54" s="65"/>
+      <c r="AC54" s="65">
         <v>1000</v>
       </c>
-      <c r="AD54" s="70"/>
-      <c r="AE54" s="70"/>
-      <c r="AF54" s="70"/>
-      <c r="AG54" s="71">
+      <c r="AD54" s="65"/>
+      <c r="AE54" s="65"/>
+      <c r="AF54" s="65"/>
+      <c r="AG54" s="66">
         <f>AC54-Z54</f>
         <v>0</v>
       </c>
-      <c r="AH54" s="72"/>
-      <c r="AI54" s="72"/>
-      <c r="AJ54" s="72"/>
+      <c r="AH54" s="67"/>
+      <c r="AI54" s="67"/>
+      <c r="AJ54" s="67"/>
       <c r="AK54" s="79" t="s">
         <v>134</v>
       </c>
@@ -13951,1188 +14204,1188 @@
       <c r="AN54" s="79"/>
     </row>
     <row r="55" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="69"/>
-      <c r="E55" s="70">
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="65">
         <v>2000</v>
       </c>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70">
+      <c r="F55" s="65"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65">
         <v>1300</v>
       </c>
-      <c r="I55" s="70"/>
-      <c r="J55" s="70"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="71">
+      <c r="I55" s="65"/>
+      <c r="J55" s="65"/>
+      <c r="K55" s="65"/>
+      <c r="L55" s="66">
         <f t="shared" ref="L55:L71" si="6">E55-H55</f>
         <v>700</v>
       </c>
-      <c r="M55" s="72"/>
-      <c r="N55" s="72"/>
-      <c r="O55" s="72"/>
-      <c r="P55" s="73" t="s">
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q55" s="73"/>
-      <c r="R55" s="73"/>
-      <c r="S55" s="73"/>
-      <c r="U55" s="67" t="s">
+      <c r="Q55" s="68"/>
+      <c r="R55" s="68"/>
+      <c r="S55" s="68"/>
+      <c r="U55" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="V55" s="68"/>
-      <c r="W55" s="68"/>
-      <c r="X55" s="69"/>
+      <c r="V55" s="63"/>
+      <c r="W55" s="63"/>
+      <c r="X55" s="64"/>
       <c r="Y55" s="47">
         <v>2000</v>
       </c>
-      <c r="Z55" s="70">
+      <c r="Z55" s="65">
         <v>2000</v>
       </c>
-      <c r="AA55" s="70"/>
-      <c r="AB55" s="70"/>
+      <c r="AA55" s="65"/>
+      <c r="AB55" s="65"/>
       <c r="AC55" s="57">
         <v>2200</v>
       </c>
       <c r="AD55" s="58"/>
       <c r="AE55" s="58"/>
       <c r="AF55" s="59"/>
-      <c r="AG55" s="71">
+      <c r="AG55" s="66">
         <f t="shared" ref="AG55:AG71" si="7">AC55-Z55</f>
         <v>200</v>
       </c>
-      <c r="AH55" s="72"/>
-      <c r="AI55" s="72"/>
-      <c r="AJ55" s="72"/>
-      <c r="AK55" s="73" t="s">
+      <c r="AH55" s="67"/>
+      <c r="AI55" s="67"/>
+      <c r="AJ55" s="67"/>
+      <c r="AK55" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL55" s="73"/>
-      <c r="AM55" s="73"/>
-      <c r="AN55" s="73"/>
+      <c r="AL55" s="68"/>
+      <c r="AM55" s="68"/>
+      <c r="AN55" s="68"/>
     </row>
     <row r="56" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="69"/>
-      <c r="E56" s="70">
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="65">
         <v>3000</v>
       </c>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70">
+      <c r="F56" s="65"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="65">
         <v>1400</v>
       </c>
-      <c r="I56" s="70"/>
-      <c r="J56" s="70"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="71">
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
+      <c r="K56" s="65"/>
+      <c r="L56" s="66">
         <f t="shared" si="6"/>
         <v>1600</v>
       </c>
-      <c r="M56" s="72"/>
-      <c r="N56" s="72"/>
-      <c r="O56" s="72"/>
-      <c r="P56" s="73" t="s">
+      <c r="M56" s="67"/>
+      <c r="N56" s="67"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q56" s="73"/>
-      <c r="R56" s="73"/>
-      <c r="S56" s="73"/>
-      <c r="U56" s="67" t="s">
+      <c r="Q56" s="68"/>
+      <c r="R56" s="68"/>
+      <c r="S56" s="68"/>
+      <c r="U56" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="V56" s="68"/>
-      <c r="W56" s="68"/>
-      <c r="X56" s="69"/>
+      <c r="V56" s="63"/>
+      <c r="W56" s="63"/>
+      <c r="X56" s="64"/>
       <c r="Y56" s="47">
         <v>3000</v>
       </c>
-      <c r="Z56" s="70">
+      <c r="Z56" s="65">
         <v>3000</v>
       </c>
-      <c r="AA56" s="70"/>
-      <c r="AB56" s="70"/>
-      <c r="AC56" s="70">
+      <c r="AA56" s="65"/>
+      <c r="AB56" s="65"/>
+      <c r="AC56" s="65">
         <v>3200</v>
       </c>
-      <c r="AD56" s="70"/>
-      <c r="AE56" s="70"/>
-      <c r="AF56" s="70"/>
-      <c r="AG56" s="71">
+      <c r="AD56" s="65"/>
+      <c r="AE56" s="65"/>
+      <c r="AF56" s="65"/>
+      <c r="AG56" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH56" s="72"/>
-      <c r="AI56" s="72"/>
-      <c r="AJ56" s="72"/>
-      <c r="AK56" s="73" t="s">
+      <c r="AH56" s="67"/>
+      <c r="AI56" s="67"/>
+      <c r="AJ56" s="67"/>
+      <c r="AK56" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL56" s="73"/>
-      <c r="AM56" s="73"/>
-      <c r="AN56" s="73"/>
+      <c r="AL56" s="68"/>
+      <c r="AM56" s="68"/>
+      <c r="AN56" s="68"/>
     </row>
     <row r="57" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A57" s="67" t="s">
+      <c r="A57" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="70">
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="64"/>
+      <c r="E57" s="65">
         <v>4000</v>
       </c>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70">
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65">
         <v>1500</v>
       </c>
-      <c r="I57" s="70"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="71">
+      <c r="I57" s="65"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="66">
         <f t="shared" si="6"/>
         <v>2500</v>
       </c>
-      <c r="M57" s="72"/>
-      <c r="N57" s="72"/>
-      <c r="O57" s="72"/>
-      <c r="P57" s="73" t="s">
+      <c r="M57" s="67"/>
+      <c r="N57" s="67"/>
+      <c r="O57" s="67"/>
+      <c r="P57" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q57" s="73"/>
-      <c r="R57" s="73"/>
-      <c r="S57" s="73"/>
-      <c r="U57" s="67" t="s">
+      <c r="Q57" s="68"/>
+      <c r="R57" s="68"/>
+      <c r="S57" s="68"/>
+      <c r="U57" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="V57" s="68"/>
-      <c r="W57" s="68"/>
-      <c r="X57" s="69"/>
+      <c r="V57" s="63"/>
+      <c r="W57" s="63"/>
+      <c r="X57" s="64"/>
       <c r="Y57" s="47">
         <v>4000</v>
       </c>
-      <c r="Z57" s="70">
+      <c r="Z57" s="65">
         <v>4000</v>
       </c>
-      <c r="AA57" s="70"/>
-      <c r="AB57" s="70"/>
-      <c r="AC57" s="70">
+      <c r="AA57" s="65"/>
+      <c r="AB57" s="65"/>
+      <c r="AC57" s="65">
         <v>4200</v>
       </c>
-      <c r="AD57" s="70"/>
-      <c r="AE57" s="70"/>
-      <c r="AF57" s="70"/>
-      <c r="AG57" s="71">
+      <c r="AD57" s="65"/>
+      <c r="AE57" s="65"/>
+      <c r="AF57" s="65"/>
+      <c r="AG57" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH57" s="72"/>
-      <c r="AI57" s="72"/>
-      <c r="AJ57" s="72"/>
-      <c r="AK57" s="73" t="s">
+      <c r="AH57" s="67"/>
+      <c r="AI57" s="67"/>
+      <c r="AJ57" s="67"/>
+      <c r="AK57" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL57" s="73"/>
-      <c r="AM57" s="73"/>
-      <c r="AN57" s="73"/>
+      <c r="AL57" s="68"/>
+      <c r="AM57" s="68"/>
+      <c r="AN57" s="68"/>
     </row>
     <row r="58" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="70">
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="65">
         <v>5000</v>
       </c>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70">
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65">
         <v>1600</v>
       </c>
-      <c r="I58" s="70"/>
-      <c r="J58" s="70"/>
-      <c r="K58" s="70"/>
-      <c r="L58" s="71">
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="66">
         <f t="shared" si="6"/>
         <v>3400</v>
       </c>
-      <c r="M58" s="72"/>
-      <c r="N58" s="72"/>
-      <c r="O58" s="72"/>
-      <c r="P58" s="73" t="s">
+      <c r="M58" s="67"/>
+      <c r="N58" s="67"/>
+      <c r="O58" s="67"/>
+      <c r="P58" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="73"/>
-      <c r="S58" s="73"/>
-      <c r="U58" s="67" t="s">
+      <c r="Q58" s="68"/>
+      <c r="R58" s="68"/>
+      <c r="S58" s="68"/>
+      <c r="U58" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="V58" s="68"/>
-      <c r="W58" s="68"/>
-      <c r="X58" s="69"/>
+      <c r="V58" s="63"/>
+      <c r="W58" s="63"/>
+      <c r="X58" s="64"/>
       <c r="Y58" s="47">
         <v>5000</v>
       </c>
-      <c r="Z58" s="70">
+      <c r="Z58" s="65">
         <v>5000</v>
       </c>
-      <c r="AA58" s="70"/>
-      <c r="AB58" s="70"/>
+      <c r="AA58" s="65"/>
+      <c r="AB58" s="65"/>
       <c r="AC58" s="57">
         <v>5200</v>
       </c>
       <c r="AD58" s="58"/>
       <c r="AE58" s="58"/>
       <c r="AF58" s="59"/>
-      <c r="AG58" s="71">
+      <c r="AG58" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH58" s="72"/>
-      <c r="AI58" s="72"/>
-      <c r="AJ58" s="72"/>
-      <c r="AK58" s="73" t="s">
+      <c r="AH58" s="67"/>
+      <c r="AI58" s="67"/>
+      <c r="AJ58" s="67"/>
+      <c r="AK58" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL58" s="73"/>
-      <c r="AM58" s="73"/>
-      <c r="AN58" s="73"/>
+      <c r="AL58" s="68"/>
+      <c r="AM58" s="68"/>
+      <c r="AN58" s="68"/>
     </row>
     <row r="59" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="69"/>
-      <c r="E59" s="70">
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="64"/>
+      <c r="E59" s="65">
         <v>6000</v>
       </c>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70">
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65">
         <v>1700</v>
       </c>
-      <c r="I59" s="70"/>
-      <c r="J59" s="70"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="71">
+      <c r="I59" s="65"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="66">
         <f t="shared" si="6"/>
         <v>4300</v>
       </c>
-      <c r="M59" s="72"/>
-      <c r="N59" s="72"/>
-      <c r="O59" s="72"/>
-      <c r="P59" s="73" t="s">
+      <c r="M59" s="67"/>
+      <c r="N59" s="67"/>
+      <c r="O59" s="67"/>
+      <c r="P59" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q59" s="73"/>
-      <c r="R59" s="73"/>
-      <c r="S59" s="73"/>
-      <c r="U59" s="67" t="s">
+      <c r="Q59" s="68"/>
+      <c r="R59" s="68"/>
+      <c r="S59" s="68"/>
+      <c r="U59" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="V59" s="68"/>
-      <c r="W59" s="68"/>
-      <c r="X59" s="69"/>
+      <c r="V59" s="63"/>
+      <c r="W59" s="63"/>
+      <c r="X59" s="64"/>
       <c r="Y59" s="47">
         <v>6000</v>
       </c>
-      <c r="Z59" s="70">
+      <c r="Z59" s="65">
         <v>6000</v>
       </c>
-      <c r="AA59" s="70"/>
-      <c r="AB59" s="70"/>
-      <c r="AC59" s="70">
+      <c r="AA59" s="65"/>
+      <c r="AB59" s="65"/>
+      <c r="AC59" s="65">
         <v>6200</v>
       </c>
-      <c r="AD59" s="70"/>
-      <c r="AE59" s="70"/>
-      <c r="AF59" s="70"/>
-      <c r="AG59" s="71">
+      <c r="AD59" s="65"/>
+      <c r="AE59" s="65"/>
+      <c r="AF59" s="65"/>
+      <c r="AG59" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH59" s="72"/>
-      <c r="AI59" s="72"/>
-      <c r="AJ59" s="72"/>
-      <c r="AK59" s="73" t="s">
+      <c r="AH59" s="67"/>
+      <c r="AI59" s="67"/>
+      <c r="AJ59" s="67"/>
+      <c r="AK59" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL59" s="73"/>
-      <c r="AM59" s="73"/>
-      <c r="AN59" s="73"/>
+      <c r="AL59" s="68"/>
+      <c r="AM59" s="68"/>
+      <c r="AN59" s="68"/>
     </row>
     <row r="60" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="70">
+      <c r="B60" s="63"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="65">
         <v>7000</v>
       </c>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70">
+      <c r="F60" s="65"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65">
         <v>1800</v>
       </c>
-      <c r="I60" s="70"/>
-      <c r="J60" s="70"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="71">
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="65"/>
+      <c r="L60" s="66">
         <f t="shared" si="6"/>
         <v>5200</v>
       </c>
-      <c r="M60" s="72"/>
-      <c r="N60" s="72"/>
-      <c r="O60" s="72"/>
-      <c r="P60" s="73" t="s">
+      <c r="M60" s="67"/>
+      <c r="N60" s="67"/>
+      <c r="O60" s="67"/>
+      <c r="P60" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q60" s="73"/>
-      <c r="R60" s="73"/>
-      <c r="S60" s="73"/>
-      <c r="U60" s="67" t="s">
+      <c r="Q60" s="68"/>
+      <c r="R60" s="68"/>
+      <c r="S60" s="68"/>
+      <c r="U60" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="V60" s="68"/>
-      <c r="W60" s="68"/>
-      <c r="X60" s="69"/>
+      <c r="V60" s="63"/>
+      <c r="W60" s="63"/>
+      <c r="X60" s="64"/>
       <c r="Y60" s="47">
         <v>7000</v>
       </c>
-      <c r="Z60" s="70">
+      <c r="Z60" s="65">
         <v>7000</v>
       </c>
-      <c r="AA60" s="70"/>
-      <c r="AB60" s="70"/>
-      <c r="AC60" s="70">
+      <c r="AA60" s="65"/>
+      <c r="AB60" s="65"/>
+      <c r="AC60" s="65">
         <v>8000</v>
       </c>
-      <c r="AD60" s="70"/>
-      <c r="AE60" s="70"/>
-      <c r="AF60" s="70"/>
-      <c r="AG60" s="71">
+      <c r="AD60" s="65"/>
+      <c r="AE60" s="65"/>
+      <c r="AF60" s="65"/>
+      <c r="AG60" s="66">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="AH60" s="72"/>
-      <c r="AI60" s="72"/>
-      <c r="AJ60" s="72"/>
-      <c r="AK60" s="73" t="s">
+      <c r="AH60" s="67"/>
+      <c r="AI60" s="67"/>
+      <c r="AJ60" s="67"/>
+      <c r="AK60" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL60" s="73"/>
-      <c r="AM60" s="73"/>
-      <c r="AN60" s="73"/>
+      <c r="AL60" s="68"/>
+      <c r="AM60" s="68"/>
+      <c r="AN60" s="68"/>
     </row>
     <row r="61" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="70">
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="64"/>
+      <c r="E61" s="65">
         <v>8000</v>
       </c>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70">
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65">
         <v>1900</v>
       </c>
-      <c r="I61" s="70"/>
-      <c r="J61" s="70"/>
-      <c r="K61" s="70"/>
-      <c r="L61" s="71">
+      <c r="I61" s="65"/>
+      <c r="J61" s="65"/>
+      <c r="K61" s="65"/>
+      <c r="L61" s="66">
         <f t="shared" si="6"/>
         <v>6100</v>
       </c>
-      <c r="M61" s="72"/>
-      <c r="N61" s="72"/>
-      <c r="O61" s="72"/>
-      <c r="P61" s="73" t="s">
+      <c r="M61" s="67"/>
+      <c r="N61" s="67"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q61" s="73"/>
-      <c r="R61" s="73"/>
-      <c r="S61" s="73"/>
-      <c r="U61" s="67" t="s">
+      <c r="Q61" s="68"/>
+      <c r="R61" s="68"/>
+      <c r="S61" s="68"/>
+      <c r="U61" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="V61" s="68"/>
-      <c r="W61" s="68"/>
-      <c r="X61" s="69"/>
+      <c r="V61" s="63"/>
+      <c r="W61" s="63"/>
+      <c r="X61" s="64"/>
       <c r="Y61" s="47">
         <v>8000</v>
       </c>
-      <c r="Z61" s="70">
+      <c r="Z61" s="65">
         <v>8000</v>
       </c>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="70"/>
+      <c r="AA61" s="65"/>
+      <c r="AB61" s="65"/>
       <c r="AC61" s="57">
         <v>8200</v>
       </c>
       <c r="AD61" s="58"/>
       <c r="AE61" s="58"/>
       <c r="AF61" s="59"/>
-      <c r="AG61" s="71">
+      <c r="AG61" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH61" s="72"/>
-      <c r="AI61" s="72"/>
-      <c r="AJ61" s="72"/>
-      <c r="AK61" s="73" t="s">
+      <c r="AH61" s="67"/>
+      <c r="AI61" s="67"/>
+      <c r="AJ61" s="67"/>
+      <c r="AK61" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL61" s="73"/>
-      <c r="AM61" s="73"/>
-      <c r="AN61" s="73"/>
+      <c r="AL61" s="68"/>
+      <c r="AM61" s="68"/>
+      <c r="AN61" s="68"/>
     </row>
     <row r="62" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A62" s="67" t="s">
+      <c r="A62" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70">
+      <c r="B62" s="63"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="64"/>
+      <c r="E62" s="65">
         <v>9000</v>
       </c>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="70">
+      <c r="F62" s="65"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="65">
         <v>2000</v>
       </c>
-      <c r="I62" s="70"/>
-      <c r="J62" s="70"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="71">
+      <c r="I62" s="65"/>
+      <c r="J62" s="65"/>
+      <c r="K62" s="65"/>
+      <c r="L62" s="66">
         <f t="shared" si="6"/>
         <v>7000</v>
       </c>
-      <c r="M62" s="72"/>
-      <c r="N62" s="72"/>
-      <c r="O62" s="72"/>
-      <c r="P62" s="73" t="s">
+      <c r="M62" s="67"/>
+      <c r="N62" s="67"/>
+      <c r="O62" s="67"/>
+      <c r="P62" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="73"/>
-      <c r="R62" s="73"/>
-      <c r="S62" s="73"/>
-      <c r="U62" s="67" t="s">
+      <c r="Q62" s="68"/>
+      <c r="R62" s="68"/>
+      <c r="S62" s="68"/>
+      <c r="U62" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="V62" s="68"/>
-      <c r="W62" s="68"/>
-      <c r="X62" s="69"/>
+      <c r="V62" s="63"/>
+      <c r="W62" s="63"/>
+      <c r="X62" s="64"/>
       <c r="Y62" s="47">
         <v>9000</v>
       </c>
-      <c r="Z62" s="70">
+      <c r="Z62" s="65">
         <v>9000</v>
       </c>
-      <c r="AA62" s="70"/>
-      <c r="AB62" s="70"/>
-      <c r="AC62" s="70">
+      <c r="AA62" s="65"/>
+      <c r="AB62" s="65"/>
+      <c r="AC62" s="65">
         <v>10000</v>
       </c>
-      <c r="AD62" s="70"/>
-      <c r="AE62" s="70"/>
-      <c r="AF62" s="70"/>
-      <c r="AG62" s="71">
+      <c r="AD62" s="65"/>
+      <c r="AE62" s="65"/>
+      <c r="AF62" s="65"/>
+      <c r="AG62" s="66">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="AH62" s="72"/>
-      <c r="AI62" s="72"/>
-      <c r="AJ62" s="72"/>
-      <c r="AK62" s="73" t="s">
+      <c r="AH62" s="67"/>
+      <c r="AI62" s="67"/>
+      <c r="AJ62" s="67"/>
+      <c r="AK62" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL62" s="73"/>
-      <c r="AM62" s="73"/>
-      <c r="AN62" s="73"/>
+      <c r="AL62" s="68"/>
+      <c r="AM62" s="68"/>
+      <c r="AN62" s="68"/>
     </row>
     <row r="63" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A63" s="67" t="s">
+      <c r="A63" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="70">
+      <c r="B63" s="63"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="64"/>
+      <c r="E63" s="65">
         <v>10000</v>
       </c>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
-      <c r="H63" s="70">
+      <c r="F63" s="65"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="65">
         <v>22100</v>
       </c>
-      <c r="I63" s="70"/>
-      <c r="J63" s="70"/>
-      <c r="K63" s="70"/>
-      <c r="L63" s="71">
+      <c r="I63" s="65"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="65"/>
+      <c r="L63" s="66">
         <f t="shared" si="6"/>
         <v>-12100</v>
       </c>
-      <c r="M63" s="72"/>
-      <c r="N63" s="72"/>
-      <c r="O63" s="72"/>
+      <c r="M63" s="67"/>
+      <c r="N63" s="67"/>
+      <c r="O63" s="67"/>
       <c r="P63" s="79" t="s">
         <v>101</v>
       </c>
       <c r="Q63" s="79"/>
       <c r="R63" s="79"/>
       <c r="S63" s="79"/>
-      <c r="U63" s="67" t="s">
+      <c r="U63" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="V63" s="68"/>
-      <c r="W63" s="68"/>
-      <c r="X63" s="69"/>
+      <c r="V63" s="63"/>
+      <c r="W63" s="63"/>
+      <c r="X63" s="64"/>
       <c r="Y63" s="47">
         <v>10000</v>
       </c>
-      <c r="Z63" s="70">
+      <c r="Z63" s="65">
         <v>10000</v>
       </c>
-      <c r="AA63" s="70"/>
-      <c r="AB63" s="70"/>
-      <c r="AC63" s="70">
+      <c r="AA63" s="65"/>
+      <c r="AB63" s="65"/>
+      <c r="AC63" s="65">
         <v>10200</v>
       </c>
-      <c r="AD63" s="70"/>
-      <c r="AE63" s="70"/>
-      <c r="AF63" s="70"/>
-      <c r="AG63" s="71">
+      <c r="AD63" s="65"/>
+      <c r="AE63" s="65"/>
+      <c r="AF63" s="65"/>
+      <c r="AG63" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH63" s="72"/>
-      <c r="AI63" s="72"/>
-      <c r="AJ63" s="72"/>
-      <c r="AK63" s="73" t="s">
+      <c r="AH63" s="67"/>
+      <c r="AI63" s="67"/>
+      <c r="AJ63" s="67"/>
+      <c r="AK63" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL63" s="73"/>
-      <c r="AM63" s="73"/>
-      <c r="AN63" s="73"/>
+      <c r="AL63" s="68"/>
+      <c r="AM63" s="68"/>
+      <c r="AN63" s="68"/>
     </row>
     <row r="64" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="70">
+      <c r="B64" s="63"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="64"/>
+      <c r="E64" s="65">
         <v>11000</v>
       </c>
-      <c r="F64" s="70"/>
-      <c r="G64" s="70"/>
-      <c r="H64" s="70">
+      <c r="F64" s="65"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="65">
         <v>2200</v>
       </c>
-      <c r="I64" s="70"/>
-      <c r="J64" s="70"/>
-      <c r="K64" s="70"/>
-      <c r="L64" s="71">
+      <c r="I64" s="65"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="65"/>
+      <c r="L64" s="66">
         <f t="shared" si="6"/>
         <v>8800</v>
       </c>
-      <c r="M64" s="72"/>
-      <c r="N64" s="72"/>
-      <c r="O64" s="72"/>
-      <c r="P64" s="73" t="s">
+      <c r="M64" s="67"/>
+      <c r="N64" s="67"/>
+      <c r="O64" s="67"/>
+      <c r="P64" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q64" s="73"/>
-      <c r="R64" s="73"/>
-      <c r="S64" s="73"/>
-      <c r="U64" s="67" t="s">
+      <c r="Q64" s="68"/>
+      <c r="R64" s="68"/>
+      <c r="S64" s="68"/>
+      <c r="U64" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="V64" s="68"/>
-      <c r="W64" s="68"/>
-      <c r="X64" s="69"/>
+      <c r="V64" s="63"/>
+      <c r="W64" s="63"/>
+      <c r="X64" s="64"/>
       <c r="Y64" s="47">
         <v>11000</v>
       </c>
-      <c r="Z64" s="70">
+      <c r="Z64" s="65">
         <v>11000</v>
       </c>
-      <c r="AA64" s="70"/>
-      <c r="AB64" s="70"/>
+      <c r="AA64" s="65"/>
+      <c r="AB64" s="65"/>
       <c r="AC64" s="57">
         <v>11200</v>
       </c>
       <c r="AD64" s="58"/>
       <c r="AE64" s="58"/>
       <c r="AF64" s="59"/>
-      <c r="AG64" s="71">
+      <c r="AG64" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH64" s="72"/>
-      <c r="AI64" s="72"/>
-      <c r="AJ64" s="72"/>
-      <c r="AK64" s="73" t="s">
+      <c r="AH64" s="67"/>
+      <c r="AI64" s="67"/>
+      <c r="AJ64" s="67"/>
+      <c r="AK64" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL64" s="73"/>
-      <c r="AM64" s="73"/>
-      <c r="AN64" s="73"/>
+      <c r="AL64" s="68"/>
+      <c r="AM64" s="68"/>
+      <c r="AN64" s="68"/>
     </row>
     <row r="65" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="67" t="s">
+      <c r="A65" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="B65" s="68"/>
-      <c r="C65" s="68"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="70">
+      <c r="B65" s="63"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="64"/>
+      <c r="E65" s="65">
         <v>12000</v>
       </c>
-      <c r="F65" s="70"/>
-      <c r="G65" s="70"/>
-      <c r="H65" s="70">
+      <c r="F65" s="65"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65">
         <v>22300</v>
       </c>
-      <c r="I65" s="70"/>
-      <c r="J65" s="70"/>
-      <c r="K65" s="70"/>
-      <c r="L65" s="71">
+      <c r="I65" s="65"/>
+      <c r="J65" s="65"/>
+      <c r="K65" s="65"/>
+      <c r="L65" s="66">
         <f t="shared" si="6"/>
         <v>-10300</v>
       </c>
-      <c r="M65" s="72"/>
-      <c r="N65" s="72"/>
-      <c r="O65" s="72"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="67"/>
+      <c r="O65" s="67"/>
       <c r="P65" s="79" t="s">
         <v>101</v>
       </c>
       <c r="Q65" s="79"/>
       <c r="R65" s="79"/>
       <c r="S65" s="79"/>
-      <c r="U65" s="67" t="s">
+      <c r="U65" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="V65" s="68"/>
-      <c r="W65" s="68"/>
-      <c r="X65" s="69"/>
+      <c r="V65" s="63"/>
+      <c r="W65" s="63"/>
+      <c r="X65" s="64"/>
       <c r="Y65" s="47">
         <v>12000</v>
       </c>
-      <c r="Z65" s="70">
+      <c r="Z65" s="65">
         <v>12000</v>
       </c>
-      <c r="AA65" s="70"/>
-      <c r="AB65" s="70"/>
-      <c r="AC65" s="70">
+      <c r="AA65" s="65"/>
+      <c r="AB65" s="65"/>
+      <c r="AC65" s="65">
         <v>20000</v>
       </c>
-      <c r="AD65" s="70"/>
-      <c r="AE65" s="70"/>
-      <c r="AF65" s="70"/>
-      <c r="AG65" s="71">
+      <c r="AD65" s="65"/>
+      <c r="AE65" s="65"/>
+      <c r="AF65" s="65"/>
+      <c r="AG65" s="66">
         <f t="shared" si="7"/>
         <v>8000</v>
       </c>
-      <c r="AH65" s="72"/>
-      <c r="AI65" s="72"/>
-      <c r="AJ65" s="72"/>
-      <c r="AK65" s="73" t="s">
+      <c r="AH65" s="67"/>
+      <c r="AI65" s="67"/>
+      <c r="AJ65" s="67"/>
+      <c r="AK65" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL65" s="73"/>
-      <c r="AM65" s="73"/>
-      <c r="AN65" s="73"/>
+      <c r="AL65" s="68"/>
+      <c r="AM65" s="68"/>
+      <c r="AN65" s="68"/>
     </row>
     <row r="66" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A66" s="67" t="s">
+      <c r="A66" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="70">
+      <c r="B66" s="63"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="65">
         <v>13000</v>
       </c>
-      <c r="F66" s="70"/>
-      <c r="G66" s="70"/>
-      <c r="H66" s="70">
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="65">
         <v>22400</v>
       </c>
-      <c r="I66" s="70"/>
-      <c r="J66" s="70"/>
-      <c r="K66" s="70"/>
-      <c r="L66" s="71">
+      <c r="I66" s="65"/>
+      <c r="J66" s="65"/>
+      <c r="K66" s="65"/>
+      <c r="L66" s="66">
         <f t="shared" si="6"/>
         <v>-9400</v>
       </c>
-      <c r="M66" s="72"/>
-      <c r="N66" s="72"/>
-      <c r="O66" s="72"/>
+      <c r="M66" s="67"/>
+      <c r="N66" s="67"/>
+      <c r="O66" s="67"/>
       <c r="P66" s="79" t="s">
         <v>101</v>
       </c>
       <c r="Q66" s="79"/>
       <c r="R66" s="79"/>
       <c r="S66" s="79"/>
-      <c r="U66" s="67" t="s">
+      <c r="U66" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="V66" s="68"/>
-      <c r="W66" s="68"/>
-      <c r="X66" s="69"/>
+      <c r="V66" s="63"/>
+      <c r="W66" s="63"/>
+      <c r="X66" s="64"/>
       <c r="Y66" s="47">
         <v>13000</v>
       </c>
-      <c r="Z66" s="70">
+      <c r="Z66" s="65">
         <v>13000</v>
       </c>
-      <c r="AA66" s="70"/>
-      <c r="AB66" s="70"/>
-      <c r="AC66" s="70">
+      <c r="AA66" s="65"/>
+      <c r="AB66" s="65"/>
+      <c r="AC66" s="65">
         <v>13200</v>
       </c>
-      <c r="AD66" s="70"/>
-      <c r="AE66" s="70"/>
-      <c r="AF66" s="70"/>
-      <c r="AG66" s="71">
+      <c r="AD66" s="65"/>
+      <c r="AE66" s="65"/>
+      <c r="AF66" s="65"/>
+      <c r="AG66" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH66" s="72"/>
-      <c r="AI66" s="72"/>
-      <c r="AJ66" s="72"/>
-      <c r="AK66" s="73" t="s">
+      <c r="AH66" s="67"/>
+      <c r="AI66" s="67"/>
+      <c r="AJ66" s="67"/>
+      <c r="AK66" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL66" s="73"/>
-      <c r="AM66" s="73"/>
-      <c r="AN66" s="73"/>
+      <c r="AL66" s="68"/>
+      <c r="AM66" s="68"/>
+      <c r="AN66" s="68"/>
     </row>
     <row r="67" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="69"/>
-      <c r="E67" s="70">
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="64"/>
+      <c r="E67" s="65">
         <v>14000</v>
       </c>
-      <c r="F67" s="70"/>
-      <c r="G67" s="70"/>
-      <c r="H67" s="70">
+      <c r="F67" s="65"/>
+      <c r="G67" s="65"/>
+      <c r="H67" s="65">
         <v>2500</v>
       </c>
-      <c r="I67" s="70"/>
-      <c r="J67" s="70"/>
-      <c r="K67" s="70"/>
-      <c r="L67" s="71">
+      <c r="I67" s="65"/>
+      <c r="J67" s="65"/>
+      <c r="K67" s="65"/>
+      <c r="L67" s="66">
         <f t="shared" si="6"/>
         <v>11500</v>
       </c>
-      <c r="M67" s="72"/>
-      <c r="N67" s="72"/>
-      <c r="O67" s="72"/>
-      <c r="P67" s="73" t="s">
+      <c r="M67" s="67"/>
+      <c r="N67" s="67"/>
+      <c r="O67" s="67"/>
+      <c r="P67" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q67" s="73"/>
-      <c r="R67" s="73"/>
-      <c r="S67" s="73"/>
-      <c r="U67" s="67" t="s">
+      <c r="Q67" s="68"/>
+      <c r="R67" s="68"/>
+      <c r="S67" s="68"/>
+      <c r="U67" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="V67" s="68"/>
-      <c r="W67" s="68"/>
-      <c r="X67" s="69"/>
+      <c r="V67" s="63"/>
+      <c r="W67" s="63"/>
+      <c r="X67" s="64"/>
       <c r="Y67" s="47">
         <v>14000</v>
       </c>
-      <c r="Z67" s="70">
+      <c r="Z67" s="65">
         <v>14000</v>
       </c>
-      <c r="AA67" s="70"/>
-      <c r="AB67" s="70"/>
+      <c r="AA67" s="65"/>
+      <c r="AB67" s="65"/>
       <c r="AC67" s="57">
         <v>23000</v>
       </c>
       <c r="AD67" s="58"/>
       <c r="AE67" s="58"/>
       <c r="AF67" s="59"/>
-      <c r="AG67" s="71">
+      <c r="AG67" s="66">
         <f t="shared" si="7"/>
         <v>9000</v>
       </c>
-      <c r="AH67" s="72"/>
-      <c r="AI67" s="72"/>
-      <c r="AJ67" s="72"/>
-      <c r="AK67" s="73" t="s">
+      <c r="AH67" s="67"/>
+      <c r="AI67" s="67"/>
+      <c r="AJ67" s="67"/>
+      <c r="AK67" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL67" s="73"/>
-      <c r="AM67" s="73"/>
-      <c r="AN67" s="73"/>
+      <c r="AL67" s="68"/>
+      <c r="AM67" s="68"/>
+      <c r="AN67" s="68"/>
     </row>
     <row r="68" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
-      <c r="D68" s="69"/>
-      <c r="E68" s="70">
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="64"/>
+      <c r="E68" s="65">
         <v>15000</v>
       </c>
-      <c r="F68" s="70"/>
-      <c r="G68" s="70"/>
-      <c r="H68" s="70">
+      <c r="F68" s="65"/>
+      <c r="G68" s="65"/>
+      <c r="H68" s="65">
         <v>2600</v>
       </c>
-      <c r="I68" s="70"/>
-      <c r="J68" s="70"/>
-      <c r="K68" s="70"/>
-      <c r="L68" s="71">
+      <c r="I68" s="65"/>
+      <c r="J68" s="65"/>
+      <c r="K68" s="65"/>
+      <c r="L68" s="66">
         <f t="shared" si="6"/>
         <v>12400</v>
       </c>
-      <c r="M68" s="72"/>
-      <c r="N68" s="72"/>
-      <c r="O68" s="72"/>
-      <c r="P68" s="73" t="s">
+      <c r="M68" s="67"/>
+      <c r="N68" s="67"/>
+      <c r="O68" s="67"/>
+      <c r="P68" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q68" s="73"/>
-      <c r="R68" s="73"/>
-      <c r="S68" s="73"/>
-      <c r="U68" s="67" t="s">
+      <c r="Q68" s="68"/>
+      <c r="R68" s="68"/>
+      <c r="S68" s="68"/>
+      <c r="U68" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="V68" s="68"/>
-      <c r="W68" s="68"/>
-      <c r="X68" s="69"/>
+      <c r="V68" s="63"/>
+      <c r="W68" s="63"/>
+      <c r="X68" s="64"/>
       <c r="Y68" s="47">
         <v>15000</v>
       </c>
-      <c r="Z68" s="70">
+      <c r="Z68" s="65">
         <v>15000</v>
       </c>
-      <c r="AA68" s="70"/>
-      <c r="AB68" s="70"/>
-      <c r="AC68" s="70">
+      <c r="AA68" s="65"/>
+      <c r="AB68" s="65"/>
+      <c r="AC68" s="65">
         <v>15200</v>
       </c>
-      <c r="AD68" s="70"/>
-      <c r="AE68" s="70"/>
-      <c r="AF68" s="70"/>
-      <c r="AG68" s="71">
+      <c r="AD68" s="65"/>
+      <c r="AE68" s="65"/>
+      <c r="AF68" s="65"/>
+      <c r="AG68" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH68" s="72"/>
-      <c r="AI68" s="72"/>
-      <c r="AJ68" s="72"/>
-      <c r="AK68" s="73" t="s">
+      <c r="AH68" s="67"/>
+      <c r="AI68" s="67"/>
+      <c r="AJ68" s="67"/>
+      <c r="AK68" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL68" s="73"/>
-      <c r="AM68" s="73"/>
-      <c r="AN68" s="73"/>
+      <c r="AL68" s="68"/>
+      <c r="AM68" s="68"/>
+      <c r="AN68" s="68"/>
     </row>
     <row r="69" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="67" t="s">
+      <c r="A69" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="70">
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="65">
         <v>16000</v>
       </c>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70">
+      <c r="F69" s="65"/>
+      <c r="G69" s="65"/>
+      <c r="H69" s="65">
         <v>22700</v>
       </c>
-      <c r="I69" s="70"/>
-      <c r="J69" s="70"/>
-      <c r="K69" s="70"/>
-      <c r="L69" s="71">
+      <c r="I69" s="65"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="65"/>
+      <c r="L69" s="66">
         <f t="shared" si="6"/>
         <v>-6700</v>
       </c>
-      <c r="M69" s="72"/>
-      <c r="N69" s="72"/>
-      <c r="O69" s="72"/>
+      <c r="M69" s="67"/>
+      <c r="N69" s="67"/>
+      <c r="O69" s="67"/>
       <c r="P69" s="79" t="s">
         <v>101</v>
       </c>
       <c r="Q69" s="79"/>
       <c r="R69" s="79"/>
       <c r="S69" s="79"/>
-      <c r="U69" s="67" t="s">
+      <c r="U69" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="V69" s="68"/>
-      <c r="W69" s="68"/>
-      <c r="X69" s="69"/>
+      <c r="V69" s="63"/>
+      <c r="W69" s="63"/>
+      <c r="X69" s="64"/>
       <c r="Y69" s="47">
         <v>16000</v>
       </c>
-      <c r="Z69" s="70">
+      <c r="Z69" s="65">
         <v>16000</v>
       </c>
-      <c r="AA69" s="70"/>
-      <c r="AB69" s="70"/>
-      <c r="AC69" s="70">
+      <c r="AA69" s="65"/>
+      <c r="AB69" s="65"/>
+      <c r="AC69" s="65">
         <v>16200</v>
       </c>
-      <c r="AD69" s="70"/>
-      <c r="AE69" s="70"/>
-      <c r="AF69" s="70"/>
-      <c r="AG69" s="71">
+      <c r="AD69" s="65"/>
+      <c r="AE69" s="65"/>
+      <c r="AF69" s="65"/>
+      <c r="AG69" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH69" s="72"/>
-      <c r="AI69" s="72"/>
-      <c r="AJ69" s="72"/>
-      <c r="AK69" s="73" t="s">
+      <c r="AH69" s="67"/>
+      <c r="AI69" s="67"/>
+      <c r="AJ69" s="67"/>
+      <c r="AK69" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL69" s="73"/>
-      <c r="AM69" s="73"/>
-      <c r="AN69" s="73"/>
+      <c r="AL69" s="68"/>
+      <c r="AM69" s="68"/>
+      <c r="AN69" s="68"/>
     </row>
     <row r="70" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="69"/>
-      <c r="E70" s="70">
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="65">
         <v>17000</v>
       </c>
-      <c r="F70" s="70"/>
-      <c r="G70" s="70"/>
-      <c r="H70" s="70">
+      <c r="F70" s="65"/>
+      <c r="G70" s="65"/>
+      <c r="H70" s="65">
         <v>2800</v>
       </c>
-      <c r="I70" s="70"/>
-      <c r="J70" s="70"/>
-      <c r="K70" s="70"/>
-      <c r="L70" s="71">
+      <c r="I70" s="65"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="65"/>
+      <c r="L70" s="66">
         <f t="shared" si="6"/>
         <v>14200</v>
       </c>
-      <c r="M70" s="72"/>
-      <c r="N70" s="72"/>
-      <c r="O70" s="72"/>
-      <c r="P70" s="73" t="s">
+      <c r="M70" s="67"/>
+      <c r="N70" s="67"/>
+      <c r="O70" s="67"/>
+      <c r="P70" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q70" s="73"/>
-      <c r="R70" s="73"/>
-      <c r="S70" s="73"/>
-      <c r="U70" s="67" t="s">
+      <c r="Q70" s="68"/>
+      <c r="R70" s="68"/>
+      <c r="S70" s="68"/>
+      <c r="U70" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="V70" s="68"/>
-      <c r="W70" s="68"/>
-      <c r="X70" s="69"/>
+      <c r="V70" s="63"/>
+      <c r="W70" s="63"/>
+      <c r="X70" s="64"/>
       <c r="Y70" s="47">
         <v>17000</v>
       </c>
-      <c r="Z70" s="70">
+      <c r="Z70" s="65">
         <v>17000</v>
       </c>
-      <c r="AA70" s="70"/>
-      <c r="AB70" s="70"/>
+      <c r="AA70" s="65"/>
+      <c r="AB70" s="65"/>
       <c r="AC70" s="57">
         <v>17200</v>
       </c>
       <c r="AD70" s="58"/>
       <c r="AE70" s="58"/>
       <c r="AF70" s="59"/>
-      <c r="AG70" s="71">
+      <c r="AG70" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH70" s="72"/>
-      <c r="AI70" s="72"/>
-      <c r="AJ70" s="72"/>
-      <c r="AK70" s="73" t="s">
+      <c r="AH70" s="67"/>
+      <c r="AI70" s="67"/>
+      <c r="AJ70" s="67"/>
+      <c r="AK70" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL70" s="73"/>
-      <c r="AM70" s="73"/>
-      <c r="AN70" s="73"/>
+      <c r="AL70" s="68"/>
+      <c r="AM70" s="68"/>
+      <c r="AN70" s="68"/>
     </row>
     <row r="71" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="67" t="s">
+      <c r="A71" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="B71" s="68"/>
-      <c r="C71" s="68"/>
-      <c r="D71" s="69"/>
-      <c r="E71" s="70">
+      <c r="B71" s="63"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="64"/>
+      <c r="E71" s="65">
         <v>18000</v>
       </c>
-      <c r="F71" s="70"/>
-      <c r="G71" s="70"/>
-      <c r="H71" s="70">
+      <c r="F71" s="65"/>
+      <c r="G71" s="65"/>
+      <c r="H71" s="65">
         <v>2900</v>
       </c>
-      <c r="I71" s="70"/>
-      <c r="J71" s="70"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="71">
+      <c r="I71" s="65"/>
+      <c r="J71" s="65"/>
+      <c r="K71" s="65"/>
+      <c r="L71" s="66">
         <f t="shared" si="6"/>
         <v>15100</v>
       </c>
-      <c r="M71" s="72"/>
-      <c r="N71" s="72"/>
-      <c r="O71" s="72"/>
-      <c r="P71" s="73" t="s">
+      <c r="M71" s="67"/>
+      <c r="N71" s="67"/>
+      <c r="O71" s="67"/>
+      <c r="P71" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="Q71" s="73"/>
-      <c r="R71" s="73"/>
-      <c r="S71" s="73"/>
-      <c r="U71" s="67" t="s">
+      <c r="Q71" s="68"/>
+      <c r="R71" s="68"/>
+      <c r="S71" s="68"/>
+      <c r="U71" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="V71" s="68"/>
-      <c r="W71" s="68"/>
-      <c r="X71" s="69"/>
+      <c r="V71" s="63"/>
+      <c r="W71" s="63"/>
+      <c r="X71" s="64"/>
       <c r="Y71" s="47">
         <v>18000</v>
       </c>
-      <c r="Z71" s="70">
+      <c r="Z71" s="65">
         <v>18000</v>
       </c>
-      <c r="AA71" s="70"/>
-      <c r="AB71" s="70"/>
-      <c r="AC71" s="70">
+      <c r="AA71" s="65"/>
+      <c r="AB71" s="65"/>
+      <c r="AC71" s="65">
         <v>18200</v>
       </c>
-      <c r="AD71" s="70"/>
-      <c r="AE71" s="70"/>
-      <c r="AF71" s="70"/>
-      <c r="AG71" s="71">
+      <c r="AD71" s="65"/>
+      <c r="AE71" s="65"/>
+      <c r="AF71" s="65"/>
+      <c r="AG71" s="66">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AH71" s="72"/>
-      <c r="AI71" s="72"/>
-      <c r="AJ71" s="72"/>
-      <c r="AK71" s="73" t="s">
+      <c r="AH71" s="67"/>
+      <c r="AI71" s="67"/>
+      <c r="AJ71" s="67"/>
+      <c r="AK71" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AL71" s="73"/>
-      <c r="AM71" s="73"/>
-      <c r="AN71" s="73"/>
+      <c r="AL71" s="68"/>
+      <c r="AM71" s="68"/>
+      <c r="AN71" s="68"/>
     </row>
     <row r="72" spans="1:40" ht="29" x14ac:dyDescent="0.35">
-      <c r="A72" s="74"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="75">
+      <c r="A72" s="69"/>
+      <c r="B72" s="69"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="70">
         <f>AVERAGE(E54:G71)</f>
         <v>9500</v>
       </c>
-      <c r="F72" s="76"/>
-      <c r="G72" s="76"/>
-      <c r="H72" s="75">
+      <c r="F72" s="71"/>
+      <c r="G72" s="71"/>
+      <c r="H72" s="70">
         <f>AVERAGE(H54:K71)</f>
         <v>6494.4444444444443</v>
       </c>
-      <c r="I72" s="76"/>
-      <c r="J72" s="76"/>
-      <c r="K72" s="76"/>
-      <c r="L72" s="75">
+      <c r="I72" s="71"/>
+      <c r="J72" s="71"/>
+      <c r="K72" s="71"/>
+      <c r="L72" s="70">
         <f>AVERAGE(L54:O71)</f>
         <v>3005.5555555555557</v>
       </c>
-      <c r="M72" s="76"/>
-      <c r="N72" s="76"/>
-      <c r="O72" s="76"/>
-      <c r="U72" s="74"/>
-      <c r="V72" s="74"/>
-      <c r="W72" s="74"/>
-      <c r="X72" s="74"/>
+      <c r="M72" s="71"/>
+      <c r="N72" s="71"/>
+      <c r="O72" s="71"/>
+      <c r="U72" s="69"/>
+      <c r="V72" s="69"/>
+      <c r="W72" s="69"/>
+      <c r="X72" s="69"/>
       <c r="Y72" s="46"/>
-      <c r="Z72" s="75">
+      <c r="Z72" s="70">
         <f>AVERAGE(Z54:AB71)</f>
         <v>9500</v>
       </c>
-      <c r="AA72" s="76"/>
-      <c r="AB72" s="76"/>
-      <c r="AC72" s="75">
+      <c r="AA72" s="71"/>
+      <c r="AB72" s="71"/>
+      <c r="AC72" s="70">
         <f>AVERAGE(AC54:AF71)</f>
         <v>10700</v>
       </c>
-      <c r="AD72" s="76"/>
-      <c r="AE72" s="76"/>
-      <c r="AF72" s="76"/>
-      <c r="AG72" s="75">
+      <c r="AD72" s="71"/>
+      <c r="AE72" s="71"/>
+      <c r="AF72" s="71"/>
+      <c r="AG72" s="70">
         <f>AVERAGE(AG54:AJ71)</f>
         <v>1200</v>
       </c>
-      <c r="AH72" s="76"/>
-      <c r="AI72" s="76"/>
-      <c r="AJ72" s="76"/>
+      <c r="AH72" s="71"/>
+      <c r="AI72" s="71"/>
+      <c r="AJ72" s="71"/>
     </row>
     <row r="73" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="62" t="s">
+      <c r="A73" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="B73" s="62"/>
-      <c r="C73" s="62">
+      <c r="B73" s="72"/>
+      <c r="C73" s="72">
         <f>COUNTA(A54:D71)</f>
         <v>18</v>
       </c>
-      <c r="D73" s="62"/>
-      <c r="E73" s="63" t="s">
+      <c r="D73" s="72"/>
+      <c r="E73" s="73" t="s">
         <v>99</v>
       </c>
       <c r="F73" s="87">
         <f>SUM(E54:G71)</f>
         <v>171000</v>
       </c>
-      <c r="G73" s="63"/>
-      <c r="H73" s="65" t="s">
+      <c r="G73" s="73"/>
+      <c r="H73" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="I73" s="65"/>
-      <c r="J73" s="66">
+      <c r="I73" s="75"/>
+      <c r="J73" s="76">
         <f>SUM(H54:K71)</f>
         <v>116900</v>
       </c>
-      <c r="K73" s="65"/>
+      <c r="K73" s="75"/>
       <c r="L73" s="50" t="s">
         <v>102</v>
       </c>
@@ -15151,32 +15404,32 @@
         <v>Good</v>
       </c>
       <c r="S73" s="50"/>
-      <c r="U73" s="62" t="s">
+      <c r="U73" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="V73" s="62"/>
-      <c r="W73" s="62">
+      <c r="V73" s="72"/>
+      <c r="W73" s="72">
         <f>COUNTA(U54:X71)</f>
         <v>18</v>
       </c>
-      <c r="X73" s="62"/>
-      <c r="Y73" s="63" t="s">
+      <c r="X73" s="72"/>
+      <c r="Y73" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="Z73" s="64">
+      <c r="Z73" s="74">
         <f>SUM(Y54:Y71)</f>
         <v>171000</v>
       </c>
-      <c r="AA73" s="64"/>
-      <c r="AB73" s="65" t="s">
+      <c r="AA73" s="74"/>
+      <c r="AB73" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="AC73" s="65"/>
-      <c r="AD73" s="66">
+      <c r="AC73" s="75"/>
+      <c r="AD73" s="76">
         <f>SUM(Z54:AB71)</f>
         <v>171000</v>
       </c>
-      <c r="AE73" s="65"/>
+      <c r="AE73" s="75"/>
       <c r="AF73" s="50" t="s">
         <v>136</v>
       </c>
@@ -15197,17 +15450,17 @@
       <c r="AM73" s="50"/>
     </row>
     <row r="74" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="62"/>
-      <c r="B74" s="62"/>
-      <c r="C74" s="62"/>
-      <c r="D74" s="62"/>
-      <c r="E74" s="63"/>
-      <c r="F74" s="63"/>
-      <c r="G74" s="63"/>
-      <c r="H74" s="65"/>
-      <c r="I74" s="65"/>
-      <c r="J74" s="65"/>
-      <c r="K74" s="65"/>
+      <c r="A74" s="72"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="75"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="75"/>
       <c r="L74" s="50"/>
       <c r="M74" s="50"/>
       <c r="N74" s="50"/>
@@ -15216,17 +15469,17 @@
       <c r="Q74" s="50"/>
       <c r="R74" s="50"/>
       <c r="S74" s="50"/>
-      <c r="U74" s="62"/>
-      <c r="V74" s="62"/>
-      <c r="W74" s="62"/>
-      <c r="X74" s="62"/>
-      <c r="Y74" s="63"/>
-      <c r="Z74" s="64"/>
-      <c r="AA74" s="64"/>
-      <c r="AB74" s="65"/>
-      <c r="AC74" s="65"/>
-      <c r="AD74" s="65"/>
-      <c r="AE74" s="65"/>
+      <c r="U74" s="72"/>
+      <c r="V74" s="72"/>
+      <c r="W74" s="72"/>
+      <c r="X74" s="72"/>
+      <c r="Y74" s="73"/>
+      <c r="Z74" s="74"/>
+      <c r="AA74" s="74"/>
+      <c r="AB74" s="75"/>
+      <c r="AC74" s="75"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="75"/>
       <c r="AF74" s="50"/>
       <c r="AG74" s="50"/>
       <c r="AH74" s="50"/>
@@ -15320,6 +15573,901 @@
     </row>
     <row r="79" spans="1:40" ht="32" x14ac:dyDescent="0.4">
       <c r="I79" s="45"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A101" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" s="77"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="77"/>
+      <c r="H101" s="77"/>
+      <c r="I101" s="77"/>
+      <c r="J101" s="77"/>
+      <c r="K101" s="77"/>
+      <c r="L101" s="77"/>
+      <c r="M101" s="77"/>
+      <c r="N101" s="77"/>
+      <c r="O101" s="77"/>
+      <c r="P101" s="77"/>
+      <c r="Q101" s="77"/>
+      <c r="R101" s="77"/>
+      <c r="S101" s="77"/>
+      <c r="T101" s="77"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="77"/>
+      <c r="D102" s="77"/>
+      <c r="E102" s="77"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="77"/>
+      <c r="H102" s="77"/>
+      <c r="I102" s="77"/>
+      <c r="J102" s="77"/>
+      <c r="K102" s="77"/>
+      <c r="L102" s="77"/>
+      <c r="M102" s="77"/>
+      <c r="N102" s="77"/>
+      <c r="O102" s="77"/>
+      <c r="P102" s="77"/>
+      <c r="Q102" s="77"/>
+      <c r="R102" s="77"/>
+      <c r="S102" s="77"/>
+      <c r="T102" s="77"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A103" s="77"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
+      <c r="H103" s="77"/>
+      <c r="I103" s="77"/>
+      <c r="J103" s="77"/>
+      <c r="K103" s="77"/>
+      <c r="L103" s="77"/>
+      <c r="M103" s="77"/>
+      <c r="N103" s="77"/>
+      <c r="O103" s="77"/>
+      <c r="P103" s="77"/>
+      <c r="Q103" s="77"/>
+      <c r="R103" s="77"/>
+      <c r="S103" s="77"/>
+      <c r="T103" s="77"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A106" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="78"/>
+      <c r="C106" s="78"/>
+      <c r="D106" s="78"/>
+      <c r="E106" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="F106" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="G106" s="78"/>
+      <c r="H106" s="78"/>
+      <c r="I106" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="J106" s="78"/>
+      <c r="K106" s="78"/>
+      <c r="L106" s="78"/>
+      <c r="M106" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="N106" s="78"/>
+      <c r="O106" s="78"/>
+      <c r="P106" s="78"/>
+      <c r="Q106" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="R106" s="78"/>
+      <c r="S106" s="78"/>
+      <c r="T106" s="78"/>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A107" s="78"/>
+      <c r="B107" s="78"/>
+      <c r="C107" s="78"/>
+      <c r="D107" s="78"/>
+      <c r="E107" s="56"/>
+      <c r="F107" s="78"/>
+      <c r="G107" s="78"/>
+      <c r="H107" s="78"/>
+      <c r="I107" s="78"/>
+      <c r="J107" s="78"/>
+      <c r="K107" s="78"/>
+      <c r="L107" s="78"/>
+      <c r="M107" s="78"/>
+      <c r="N107" s="78"/>
+      <c r="O107" s="78"/>
+      <c r="P107" s="78"/>
+      <c r="Q107" s="78"/>
+      <c r="R107" s="78"/>
+      <c r="S107" s="78"/>
+      <c r="T107" s="78"/>
+    </row>
+    <row r="108" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A108" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B108" s="63"/>
+      <c r="C108" s="63"/>
+      <c r="D108" s="64"/>
+      <c r="E108" s="47">
+        <v>1000</v>
+      </c>
+      <c r="F108" s="65">
+        <v>1000</v>
+      </c>
+      <c r="G108" s="65"/>
+      <c r="H108" s="65"/>
+      <c r="I108" s="65">
+        <v>1000</v>
+      </c>
+      <c r="J108" s="65"/>
+      <c r="K108" s="65"/>
+      <c r="L108" s="65"/>
+      <c r="M108" s="66">
+        <f>I108-F108</f>
+        <v>0</v>
+      </c>
+      <c r="N108" s="67"/>
+      <c r="O108" s="67"/>
+      <c r="P108" s="67"/>
+      <c r="Q108" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="R108" s="79"/>
+      <c r="S108" s="79"/>
+      <c r="T108" s="79"/>
+    </row>
+    <row r="109" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B109" s="63"/>
+      <c r="C109" s="63"/>
+      <c r="D109" s="64"/>
+      <c r="E109" s="47">
+        <v>2000</v>
+      </c>
+      <c r="F109" s="65">
+        <v>2000</v>
+      </c>
+      <c r="G109" s="65"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="57">
+        <v>2200</v>
+      </c>
+      <c r="J109" s="58"/>
+      <c r="K109" s="58"/>
+      <c r="L109" s="59"/>
+      <c r="M109" s="66">
+        <f t="shared" ref="M109:M125" si="8">I109-F109</f>
+        <v>200</v>
+      </c>
+      <c r="N109" s="67"/>
+      <c r="O109" s="67"/>
+      <c r="P109" s="67"/>
+      <c r="Q109" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R109" s="68"/>
+      <c r="S109" s="68"/>
+      <c r="T109" s="68"/>
+    </row>
+    <row r="110" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A110" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B110" s="63"/>
+      <c r="C110" s="63"/>
+      <c r="D110" s="64"/>
+      <c r="E110" s="47">
+        <v>3000</v>
+      </c>
+      <c r="F110" s="65">
+        <v>3000</v>
+      </c>
+      <c r="G110" s="65"/>
+      <c r="H110" s="65"/>
+      <c r="I110" s="65">
+        <v>3200</v>
+      </c>
+      <c r="J110" s="65"/>
+      <c r="K110" s="65"/>
+      <c r="L110" s="65"/>
+      <c r="M110" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N110" s="67"/>
+      <c r="O110" s="67"/>
+      <c r="P110" s="67"/>
+      <c r="Q110" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R110" s="68"/>
+      <c r="S110" s="68"/>
+      <c r="T110" s="68"/>
+    </row>
+    <row r="111" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A111" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B111" s="63"/>
+      <c r="C111" s="63"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="47">
+        <v>4000</v>
+      </c>
+      <c r="F111" s="65">
+        <v>4000</v>
+      </c>
+      <c r="G111" s="65"/>
+      <c r="H111" s="65"/>
+      <c r="I111" s="65">
+        <v>4200</v>
+      </c>
+      <c r="J111" s="65"/>
+      <c r="K111" s="65"/>
+      <c r="L111" s="65"/>
+      <c r="M111" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N111" s="67"/>
+      <c r="O111" s="67"/>
+      <c r="P111" s="67"/>
+      <c r="Q111" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R111" s="68"/>
+      <c r="S111" s="68"/>
+      <c r="T111" s="68"/>
+    </row>
+    <row r="112" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A112" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B112" s="63"/>
+      <c r="C112" s="63"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="47">
+        <v>5000</v>
+      </c>
+      <c r="F112" s="65">
+        <v>5000</v>
+      </c>
+      <c r="G112" s="65"/>
+      <c r="H112" s="65"/>
+      <c r="I112" s="57">
+        <v>5200</v>
+      </c>
+      <c r="J112" s="58"/>
+      <c r="K112" s="58"/>
+      <c r="L112" s="59"/>
+      <c r="M112" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N112" s="67"/>
+      <c r="O112" s="67"/>
+      <c r="P112" s="67"/>
+      <c r="Q112" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R112" s="68"/>
+      <c r="S112" s="68"/>
+      <c r="T112" s="68"/>
+    </row>
+    <row r="113" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B113" s="63"/>
+      <c r="C113" s="63"/>
+      <c r="D113" s="64"/>
+      <c r="E113" s="47">
+        <v>6000</v>
+      </c>
+      <c r="F113" s="65">
+        <v>6000</v>
+      </c>
+      <c r="G113" s="65"/>
+      <c r="H113" s="65"/>
+      <c r="I113" s="65">
+        <v>6200</v>
+      </c>
+      <c r="J113" s="65"/>
+      <c r="K113" s="65"/>
+      <c r="L113" s="65"/>
+      <c r="M113" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N113" s="67"/>
+      <c r="O113" s="67"/>
+      <c r="P113" s="67"/>
+      <c r="Q113" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R113" s="68"/>
+      <c r="S113" s="68"/>
+      <c r="T113" s="68"/>
+    </row>
+    <row r="114" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B114" s="63"/>
+      <c r="C114" s="63"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="47">
+        <v>7000</v>
+      </c>
+      <c r="F114" s="65">
+        <v>7000</v>
+      </c>
+      <c r="G114" s="65"/>
+      <c r="H114" s="65"/>
+      <c r="I114" s="65">
+        <v>8000</v>
+      </c>
+      <c r="J114" s="65"/>
+      <c r="K114" s="65"/>
+      <c r="L114" s="65"/>
+      <c r="M114" s="66">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+      <c r="N114" s="67"/>
+      <c r="O114" s="67"/>
+      <c r="P114" s="67"/>
+      <c r="Q114" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R114" s="68"/>
+      <c r="S114" s="68"/>
+      <c r="T114" s="68"/>
+    </row>
+    <row r="115" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A115" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B115" s="63"/>
+      <c r="C115" s="63"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="47">
+        <v>8000</v>
+      </c>
+      <c r="F115" s="65">
+        <v>8000</v>
+      </c>
+      <c r="G115" s="65"/>
+      <c r="H115" s="65"/>
+      <c r="I115" s="57">
+        <v>8200</v>
+      </c>
+      <c r="J115" s="58"/>
+      <c r="K115" s="58"/>
+      <c r="L115" s="59"/>
+      <c r="M115" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N115" s="67"/>
+      <c r="O115" s="67"/>
+      <c r="P115" s="67"/>
+      <c r="Q115" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R115" s="68"/>
+      <c r="S115" s="68"/>
+      <c r="T115" s="68"/>
+    </row>
+    <row r="116" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B116" s="63"/>
+      <c r="C116" s="63"/>
+      <c r="D116" s="64"/>
+      <c r="E116" s="47">
+        <v>9000</v>
+      </c>
+      <c r="F116" s="65">
+        <v>9000</v>
+      </c>
+      <c r="G116" s="65"/>
+      <c r="H116" s="65"/>
+      <c r="I116" s="65">
+        <v>10000</v>
+      </c>
+      <c r="J116" s="65"/>
+      <c r="K116" s="65"/>
+      <c r="L116" s="65"/>
+      <c r="M116" s="66">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+      <c r="N116" s="67"/>
+      <c r="O116" s="67"/>
+      <c r="P116" s="67"/>
+      <c r="Q116" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R116" s="68"/>
+      <c r="S116" s="68"/>
+      <c r="T116" s="68"/>
+    </row>
+    <row r="117" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A117" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B117" s="63"/>
+      <c r="C117" s="63"/>
+      <c r="D117" s="64"/>
+      <c r="E117" s="47">
+        <v>10000</v>
+      </c>
+      <c r="F117" s="65">
+        <v>10000</v>
+      </c>
+      <c r="G117" s="65"/>
+      <c r="H117" s="65"/>
+      <c r="I117" s="65">
+        <v>10200</v>
+      </c>
+      <c r="J117" s="65"/>
+      <c r="K117" s="65"/>
+      <c r="L117" s="65"/>
+      <c r="M117" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N117" s="67"/>
+      <c r="O117" s="67"/>
+      <c r="P117" s="67"/>
+      <c r="Q117" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R117" s="68"/>
+      <c r="S117" s="68"/>
+      <c r="T117" s="68"/>
+    </row>
+    <row r="118" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="63"/>
+      <c r="C118" s="63"/>
+      <c r="D118" s="64"/>
+      <c r="E118" s="47">
+        <v>11000</v>
+      </c>
+      <c r="F118" s="65">
+        <v>11000</v>
+      </c>
+      <c r="G118" s="65"/>
+      <c r="H118" s="65"/>
+      <c r="I118" s="57">
+        <v>11200</v>
+      </c>
+      <c r="J118" s="58"/>
+      <c r="K118" s="58"/>
+      <c r="L118" s="59"/>
+      <c r="M118" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N118" s="67"/>
+      <c r="O118" s="67"/>
+      <c r="P118" s="67"/>
+      <c r="Q118" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R118" s="68"/>
+      <c r="S118" s="68"/>
+      <c r="T118" s="68"/>
+    </row>
+    <row r="119" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A119" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="63"/>
+      <c r="C119" s="63"/>
+      <c r="D119" s="64"/>
+      <c r="E119" s="47">
+        <v>12000</v>
+      </c>
+      <c r="F119" s="65">
+        <v>12000</v>
+      </c>
+      <c r="G119" s="65"/>
+      <c r="H119" s="65"/>
+      <c r="I119" s="65">
+        <v>20000</v>
+      </c>
+      <c r="J119" s="65"/>
+      <c r="K119" s="65"/>
+      <c r="L119" s="65"/>
+      <c r="M119" s="66">
+        <f t="shared" si="8"/>
+        <v>8000</v>
+      </c>
+      <c r="N119" s="67"/>
+      <c r="O119" s="67"/>
+      <c r="P119" s="67"/>
+      <c r="Q119" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R119" s="68"/>
+      <c r="S119" s="68"/>
+      <c r="T119" s="68"/>
+    </row>
+    <row r="120" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B120" s="63"/>
+      <c r="C120" s="63"/>
+      <c r="D120" s="64"/>
+      <c r="E120" s="47">
+        <v>13000</v>
+      </c>
+      <c r="F120" s="65">
+        <v>13000</v>
+      </c>
+      <c r="G120" s="65"/>
+      <c r="H120" s="65"/>
+      <c r="I120" s="65">
+        <v>13200</v>
+      </c>
+      <c r="J120" s="65"/>
+      <c r="K120" s="65"/>
+      <c r="L120" s="65"/>
+      <c r="M120" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N120" s="67"/>
+      <c r="O120" s="67"/>
+      <c r="P120" s="67"/>
+      <c r="Q120" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R120" s="68"/>
+      <c r="S120" s="68"/>
+      <c r="T120" s="68"/>
+    </row>
+    <row r="121" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B121" s="63"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="64"/>
+      <c r="E121" s="47">
+        <v>14000</v>
+      </c>
+      <c r="F121" s="65">
+        <v>14000</v>
+      </c>
+      <c r="G121" s="65"/>
+      <c r="H121" s="65"/>
+      <c r="I121" s="57">
+        <v>23000</v>
+      </c>
+      <c r="J121" s="58"/>
+      <c r="K121" s="58"/>
+      <c r="L121" s="59"/>
+      <c r="M121" s="66">
+        <f t="shared" si="8"/>
+        <v>9000</v>
+      </c>
+      <c r="N121" s="67"/>
+      <c r="O121" s="67"/>
+      <c r="P121" s="67"/>
+      <c r="Q121" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R121" s="68"/>
+      <c r="S121" s="68"/>
+      <c r="T121" s="68"/>
+    </row>
+    <row r="122" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" s="63"/>
+      <c r="C122" s="63"/>
+      <c r="D122" s="64"/>
+      <c r="E122" s="47">
+        <v>15000</v>
+      </c>
+      <c r="F122" s="65">
+        <v>15000</v>
+      </c>
+      <c r="G122" s="65"/>
+      <c r="H122" s="65"/>
+      <c r="I122" s="65">
+        <v>15200</v>
+      </c>
+      <c r="J122" s="65"/>
+      <c r="K122" s="65"/>
+      <c r="L122" s="65"/>
+      <c r="M122" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N122" s="67"/>
+      <c r="O122" s="67"/>
+      <c r="P122" s="67"/>
+      <c r="Q122" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R122" s="68"/>
+      <c r="S122" s="68"/>
+      <c r="T122" s="68"/>
+    </row>
+    <row r="123" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123" s="63"/>
+      <c r="C123" s="63"/>
+      <c r="D123" s="64"/>
+      <c r="E123" s="47">
+        <v>16000</v>
+      </c>
+      <c r="F123" s="65">
+        <v>16000</v>
+      </c>
+      <c r="G123" s="65"/>
+      <c r="H123" s="65"/>
+      <c r="I123" s="65">
+        <v>16200</v>
+      </c>
+      <c r="J123" s="65"/>
+      <c r="K123" s="65"/>
+      <c r="L123" s="65"/>
+      <c r="M123" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N123" s="67"/>
+      <c r="O123" s="67"/>
+      <c r="P123" s="67"/>
+      <c r="Q123" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R123" s="68"/>
+      <c r="S123" s="68"/>
+      <c r="T123" s="68"/>
+    </row>
+    <row r="124" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124" s="63"/>
+      <c r="C124" s="63"/>
+      <c r="D124" s="64"/>
+      <c r="E124" s="47">
+        <v>17000</v>
+      </c>
+      <c r="F124" s="65">
+        <v>17000</v>
+      </c>
+      <c r="G124" s="65"/>
+      <c r="H124" s="65"/>
+      <c r="I124" s="57">
+        <v>17200</v>
+      </c>
+      <c r="J124" s="58"/>
+      <c r="K124" s="58"/>
+      <c r="L124" s="59"/>
+      <c r="M124" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N124" s="67"/>
+      <c r="O124" s="67"/>
+      <c r="P124" s="67"/>
+      <c r="Q124" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R124" s="68"/>
+      <c r="S124" s="68"/>
+      <c r="T124" s="68"/>
+    </row>
+    <row r="125" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B125" s="63"/>
+      <c r="C125" s="63"/>
+      <c r="D125" s="64"/>
+      <c r="E125" s="47">
+        <v>18000</v>
+      </c>
+      <c r="F125" s="65">
+        <v>18000</v>
+      </c>
+      <c r="G125" s="65"/>
+      <c r="H125" s="65"/>
+      <c r="I125" s="65">
+        <v>18200</v>
+      </c>
+      <c r="J125" s="65"/>
+      <c r="K125" s="65"/>
+      <c r="L125" s="65"/>
+      <c r="M125" s="66">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="N125" s="67"/>
+      <c r="O125" s="67"/>
+      <c r="P125" s="67"/>
+      <c r="Q125" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="R125" s="68"/>
+      <c r="S125" s="68"/>
+      <c r="T125" s="68"/>
+    </row>
+    <row r="126" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="69"/>
+      <c r="B126" s="69"/>
+      <c r="C126" s="69"/>
+      <c r="D126" s="69"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="70">
+        <f>AVERAGE(F108:H125)</f>
+        <v>9500</v>
+      </c>
+      <c r="G126" s="71"/>
+      <c r="H126" s="71"/>
+      <c r="I126" s="70">
+        <f>AVERAGE(I108:L125)</f>
+        <v>10700</v>
+      </c>
+      <c r="J126" s="71"/>
+      <c r="K126" s="71"/>
+      <c r="L126" s="71"/>
+      <c r="M126" s="70">
+        <f>AVERAGE(M108:P125)</f>
+        <v>1200</v>
+      </c>
+      <c r="N126" s="71"/>
+      <c r="O126" s="71"/>
+      <c r="P126" s="71"/>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A127" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B127" s="72"/>
+      <c r="C127" s="72">
+        <f>COUNTA(A108:D125)</f>
+        <v>18</v>
+      </c>
+      <c r="D127" s="72"/>
+      <c r="E127" s="73" t="s">
+        <v>135</v>
+      </c>
+      <c r="F127" s="74">
+        <f>SUM(E108:E125)</f>
+        <v>171000</v>
+      </c>
+      <c r="G127" s="74"/>
+      <c r="H127" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="I127" s="75"/>
+      <c r="J127" s="76">
+        <f>SUM(F108:H125)</f>
+        <v>171000</v>
+      </c>
+      <c r="K127" s="75"/>
+      <c r="L127" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="M127" s="50"/>
+      <c r="N127" s="49">
+        <f>SUM(M108:P125)</f>
+        <v>21600</v>
+      </c>
+      <c r="O127" s="50"/>
+      <c r="P127" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q127" s="50"/>
+      <c r="R127" s="49" t="str">
+        <f>IF(N127&gt;0,"Profit","Loss")</f>
+        <v>Profit</v>
+      </c>
+      <c r="S127" s="50"/>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A128" s="72"/>
+      <c r="B128" s="72"/>
+      <c r="C128" s="72"/>
+      <c r="D128" s="72"/>
+      <c r="E128" s="73"/>
+      <c r="F128" s="74"/>
+      <c r="G128" s="74"/>
+      <c r="H128" s="75"/>
+      <c r="I128" s="75"/>
+      <c r="J128" s="75"/>
+      <c r="K128" s="75"/>
+      <c r="L128" s="50"/>
+      <c r="M128" s="50"/>
+      <c r="N128" s="50"/>
+      <c r="O128" s="50"/>
+      <c r="P128" s="50"/>
+      <c r="Q128" s="50"/>
+      <c r="R128" s="50"/>
+      <c r="S128" s="50"/>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A129" s="10"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="D129" s="60"/>
+      <c r="E129" s="61">
+        <f>MAX(M108:P125)</f>
+        <v>9000</v>
+      </c>
+      <c r="F129" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G129" s="51"/>
+      <c r="H129" s="51"/>
+      <c r="I129" s="52">
+        <f>_xlfn.PERCENTOF(N127,J127)</f>
+        <v>0.12631578947368421</v>
+      </c>
+      <c r="J129" s="52"/>
+      <c r="K129" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="L129" s="53"/>
+      <c r="M129" s="53"/>
+      <c r="N129" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="O129" s="54"/>
+      <c r="P129" s="48"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="C130" s="60"/>
+      <c r="D130" s="60"/>
+      <c r="E130" s="60"/>
+      <c r="F130" s="51"/>
+      <c r="G130" s="51"/>
+      <c r="H130" s="51"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="53"/>
+      <c r="L130" s="53"/>
+      <c r="M130" s="53"/>
+      <c r="N130" s="54"/>
+      <c r="O130" s="54"/>
     </row>
   </sheetData>
   <autoFilter ref="A52:AN72" xr:uid="{56183EF1-A135-7140-898B-D14C00F9AA39}">
@@ -15358,7 +16506,124 @@
     <sortCondition ref="C4:C15"/>
     <sortCondition ref="I4:I15"/>
   </sortState>
-  <mergeCells count="237">
+  <mergeCells count="354">
+    <mergeCell ref="F123:H123"/>
+    <mergeCell ref="I123:L123"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="F124:H124"/>
+    <mergeCell ref="I124:L124"/>
+    <mergeCell ref="A125:D125"/>
+    <mergeCell ref="F125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="A126:D126"/>
+    <mergeCell ref="F126:H126"/>
+    <mergeCell ref="I126:L126"/>
+    <mergeCell ref="F117:H117"/>
+    <mergeCell ref="I117:L117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="F118:H118"/>
+    <mergeCell ref="I118:L118"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="F119:H119"/>
+    <mergeCell ref="I119:L119"/>
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="F120:H120"/>
+    <mergeCell ref="I120:L120"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="F111:H111"/>
+    <mergeCell ref="I111:L111"/>
+    <mergeCell ref="M111:P111"/>
+    <mergeCell ref="Q111:T111"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="F112:H112"/>
+    <mergeCell ref="I112:L112"/>
+    <mergeCell ref="M112:P112"/>
+    <mergeCell ref="Q112:T112"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="I109:L109"/>
+    <mergeCell ref="M109:P109"/>
+    <mergeCell ref="Q109:T109"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="F110:H110"/>
+    <mergeCell ref="I110:L110"/>
+    <mergeCell ref="M110:P110"/>
+    <mergeCell ref="Q110:T110"/>
+    <mergeCell ref="A101:T103"/>
+    <mergeCell ref="A106:D107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:H107"/>
+    <mergeCell ref="I106:L107"/>
+    <mergeCell ref="M106:P107"/>
+    <mergeCell ref="Q106:T107"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="F108:H108"/>
+    <mergeCell ref="I108:L108"/>
+    <mergeCell ref="M108:P108"/>
+    <mergeCell ref="Q108:T108"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="F113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="F114:H114"/>
+    <mergeCell ref="I114:L114"/>
+    <mergeCell ref="C129:D130"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="F129:H130"/>
+    <mergeCell ref="I129:J130"/>
+    <mergeCell ref="K129:M130"/>
+    <mergeCell ref="N129:O130"/>
+    <mergeCell ref="C127:D128"/>
+    <mergeCell ref="E127:E128"/>
+    <mergeCell ref="F127:G128"/>
+    <mergeCell ref="H127:I128"/>
+    <mergeCell ref="J127:K128"/>
+    <mergeCell ref="M126:P126"/>
+    <mergeCell ref="A127:B128"/>
+    <mergeCell ref="L127:M128"/>
+    <mergeCell ref="N127:O128"/>
+    <mergeCell ref="P127:Q128"/>
+    <mergeCell ref="R127:S128"/>
+    <mergeCell ref="M124:P124"/>
+    <mergeCell ref="Q124:T124"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q125:T125"/>
+    <mergeCell ref="M122:P122"/>
+    <mergeCell ref="Q122:T122"/>
+    <mergeCell ref="M123:P123"/>
+    <mergeCell ref="Q123:T123"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="I122:L122"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="M120:P120"/>
+    <mergeCell ref="Q120:T120"/>
+    <mergeCell ref="M121:P121"/>
+    <mergeCell ref="Q121:T121"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="I121:L121"/>
+    <mergeCell ref="M118:P118"/>
+    <mergeCell ref="Q118:T118"/>
+    <mergeCell ref="M119:P119"/>
+    <mergeCell ref="Q119:T119"/>
+    <mergeCell ref="M116:P116"/>
+    <mergeCell ref="Q116:T116"/>
+    <mergeCell ref="M117:P117"/>
+    <mergeCell ref="Q117:T117"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="F116:H116"/>
+    <mergeCell ref="I116:L116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="M114:P114"/>
+    <mergeCell ref="Q114:T114"/>
+    <mergeCell ref="M115:P115"/>
+    <mergeCell ref="Q115:T115"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="F115:H115"/>
+    <mergeCell ref="I115:L115"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="Q113:T113"/>
     <mergeCell ref="A47:S49"/>
     <mergeCell ref="R73:S74"/>
     <mergeCell ref="L66:O66"/>
@@ -15405,6 +16670,8 @@
     <mergeCell ref="H69:K69"/>
     <mergeCell ref="H70:K70"/>
     <mergeCell ref="H71:K71"/>
+    <mergeCell ref="P63:S63"/>
+    <mergeCell ref="P64:S64"/>
     <mergeCell ref="E70:G70"/>
     <mergeCell ref="E71:G71"/>
     <mergeCell ref="E72:G72"/>
@@ -15426,37 +16693,9 @@
     <mergeCell ref="E67:G67"/>
     <mergeCell ref="E68:G68"/>
     <mergeCell ref="E69:G69"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="E63:G63"/>
     <mergeCell ref="E64:G64"/>
     <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="P57:S57"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="P54:S54"/>
-    <mergeCell ref="P63:S63"/>
-    <mergeCell ref="P64:S64"/>
-    <mergeCell ref="P55:S55"/>
-    <mergeCell ref="P56:S56"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:K1"/>
@@ -15466,6 +16705,21 @@
     <mergeCell ref="H75:I76"/>
     <mergeCell ref="E75:G76"/>
     <mergeCell ref="J75:L76"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="M75:N76"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="H72:K72"/>
@@ -15479,6 +16733,17 @@
     <mergeCell ref="A65:D65"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="E62:G62"/>
+    <mergeCell ref="P57:S57"/>
+    <mergeCell ref="P54:S54"/>
+    <mergeCell ref="P55:S55"/>
+    <mergeCell ref="P56:S56"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="U47:AN49"/>
     <mergeCell ref="U52:X53"/>
     <mergeCell ref="Z52:AB53"/>
@@ -15599,14 +16864,26 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D3:D15">
-    <cfRule type="iconSet" priority="30">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="iconSet" priority="51">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
         <cfvo type="percent" val="67"/>
       </iconSet>
     </cfRule>
-    <cfRule type="colorScale" priority="31">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E54:G71">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15617,8 +16894,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E54:G71">
-    <cfRule type="colorScale" priority="24">
+  <conditionalFormatting sqref="H52:K71">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15630,7 +16907,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54:K71">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15640,7 +16935,132 @@
         <color rgb="FFFF0000"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="25">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I15">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:K15">
+    <cfRule type="duplicateValues" dxfId="36" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9">
+    <cfRule type="uniqueValues" dxfId="35" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L54:O71">
+    <cfRule type="cellIs" dxfId="34" priority="43" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="42" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P54:S71">
+    <cfRule type="containsText" dxfId="32" priority="40" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="39" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",P54)))</formula>
+    </cfRule>
+    <cfRule type="iconSet" priority="49">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U52:X72">
+    <cfRule type="iconSet" priority="18">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y52:Y71">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z54:AB71">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC3:AC14">
+    <cfRule type="duplicateValues" dxfId="29" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC8">
+    <cfRule type="uniqueValues" dxfId="28" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC54:AF54 AC71:AF71 AC56:AF57 AC59:AF60 AC62:AF63 AC65:AF66 AC68:AF69">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15659,8 +17079,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I15">
-    <cfRule type="colorScale" priority="42">
+  <conditionalFormatting sqref="AC54:AF71">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15671,8 +17091,69 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
-    <cfRule type="colorScale" priority="32">
+  <conditionalFormatting sqref="AG54:AJ71">
+    <cfRule type="cellIs" dxfId="27" priority="30" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="31" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG54:AN54">
+    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK54:AN71">
+    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="29" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",AK54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="iconSet" priority="37">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="22" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",AK54)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="27" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A106:D126">
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E106:E125">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15683,57 +17164,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K15">
-    <cfRule type="duplicateValues" dxfId="15" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K9">
-    <cfRule type="uniqueValues" dxfId="14" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L54:O71">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="22" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P54:S71">
-    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",P54)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="Bad">
-      <formula>NOT(ISERROR(SEARCH("Bad",P54)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="iconSet" priority="28">
-      <iconSet>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z54:AB71">
+  <conditionalFormatting sqref="F108:H125">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -15745,14 +17176,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC14">
-    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC8">
-    <cfRule type="uniqueValues" dxfId="7" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC54:AF54 AC71:AF71 AC56:AF57 AC59:AF60 AC62:AF63 AC65:AF66 AC68:AF69">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="I108:L108 I125:L125 I110:L111 I113:L114 I116:L117 I119:L120 I122:L123">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15781,8 +17206,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC54:AF71">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="I108:L125">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15793,31 +17218,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG54:AJ71">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="M108:P125">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG54:AN54">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+  <conditionalFormatting sqref="M108:T108">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK54:AN71">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",AK54)))</formula>
+  <conditionalFormatting sqref="Q108:T125">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",Q108)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",Q108)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",AK54)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",Q108)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Bad">
-      <formula>NOT(ISERROR(SEARCH("Bad",AK54)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="Bad">
+      <formula>NOT(ISERROR(SEARCH("Bad",Q108)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="15">
       <colorScale>
